--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -20,8 +20,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -987,11 +987,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (105 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 117 řádků.</t>
+          <t>HSV položkově (106 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 118 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (187 dum + 28 sklad = 215 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (188 dum + 28 sklad = 216 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>215 (187 dum + 28 sklad)</t>
+          <t>216 (188 dum + 28 sklad)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 105 | PSV 54 | TZB 34 | VRN 22</t>
+          <t>HSV 106 | PSV 54 | TZB 34 | VRN 22</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 69 | 0.70: 1 | 0.60: 1</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 69 | 0.70: 1 | 0.60: 2</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 140 needs_production_lookup (65.1 %)</t>
+          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 140 needs_production_lookup (64.8 %)</t>
         </is>
       </c>
     </row>
@@ -1160,8 +1160,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-215 položek celkem (187 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 69×0.75 · 1×0.70 · 1×0.60.
+216 položek celkem (188 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 69×0.75 · 1×0.70 · 2×0.60.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1401,11 +1401,11 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Krokve 100/180 á 800 mm; Kleštiny 2×60/180; Pozednice 140/160; Námětky pro přesah; … (+12 dalších)</t>
+          <t>Krokve 100/180 á 800 mm; Kleštiny 2×60/180; Pozednice 140/160; Námětky pro přesah; … (+13 dalších)</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -1963,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6236,37 +6236,37 @@
       </c>
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
-        </is>
-      </c>
-      <c r="C107" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="n">
-        <v>1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="n">
+        <v>50</v>
       </c>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -6281,12 +6281,12 @@
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -6356,17 +6356,17 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
+          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C112" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C113" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="C114" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="C115" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="C116" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="C117" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="C118" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -6710,8 +6710,48 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="20" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E119" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J118"/>
+  <autoFilter ref="A1:J119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6722,7 +6762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O188"/>
+  <dimension ref="A1:O189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10604,55 +10644,55 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>962041141</t>
+          <t>762085112</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
+          <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="n">
-        <v>12</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="n">
+        <v>50</v>
       </c>
       <c r="H62" s="10" t="n"/>
       <c r="I62" s="10" t="n"/>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="K62" s="24" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="L62" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>matched_catalog</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e — 9 t dřeva celkem; krov hlavní zdroj</t>
+          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
         </is>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O62" s="26" t="inlineStr">
@@ -10672,26 +10712,26 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Bourání plechové střešní krytiny</t>
-        </is>
-      </c>
-      <c r="D63" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Bourání kompletního stávajícího krovu</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>962041141</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G63" s="22" t="n">
-        <v>140.9</v>
+        <v>12</v>
       </c>
       <c r="H63" s="10" t="n"/>
       <c r="I63" s="10" t="n"/>
@@ -10705,12 +10745,12 @@
       </c>
       <c r="L63" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e — 0.1 t kovů; stávající plech krytina</t>
+          <t>TZ B m.10.e — 9 t dřeva celkem; krov hlavní zdroj</t>
         </is>
       </c>
       <c r="N63" s="20" t="inlineStr">
@@ -10718,9 +10758,9 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="O63" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O63" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -10735,26 +10775,26 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Bourání nadezdívek nad stropem 2.NP</t>
-        </is>
-      </c>
-      <c r="D64" s="20" t="inlineStr">
-        <is>
-          <t>962031132</t>
+          <t>Bourání plechové střešní krytiny</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G64" s="22" t="n">
-        <v>6</v>
+        <v>140.9</v>
       </c>
       <c r="H64" s="10" t="n"/>
       <c r="I64" s="10" t="n"/>
@@ -10768,12 +10808,12 @@
       </c>
       <c r="L64" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — bourání nadezdívek mimo štítů</t>
+          <t>TZ B m.10.e — 0.1 t kovů; stávající plech krytina</t>
         </is>
       </c>
       <c r="N64" s="20" t="inlineStr">
@@ -10781,9 +10821,9 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="O64" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O64" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
       </c>
     </row>
@@ -10798,26 +10838,26 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Bourání trámového stropu 2.NP/podkroví</t>
+          <t>Bourání nadezdívek nad stropem 2.NP</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>962041141</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G65" s="22" t="n">
-        <v>104.4</v>
+        <v>6</v>
       </c>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="10" t="n"/>
@@ -10836,7 +10876,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — strop 2.NP/3.NP KOMPLETNĚ bourán</t>
+          <t>TZ ARS dům §3 — bourání nadezdívek mimo štítů</t>
         </is>
       </c>
       <c r="N65" s="20" t="inlineStr">
@@ -10861,17 +10901,17 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Bourání lehkých příček</t>
+          <t>Bourání trámového stropu 2.NP/podkroví</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>962031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
@@ -10880,7 +10920,7 @@
         </is>
       </c>
       <c r="G66" s="22" t="n">
-        <v>80</v>
+        <v>104.4</v>
       </c>
       <c r="H66" s="10" t="n"/>
       <c r="I66" s="10" t="n"/>
@@ -10899,7 +10939,7 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — lehké příčky bourány</t>
+          <t>TZ ARS dům §3 — strop 2.NP/3.NP KOMPLETNĚ bourán</t>
         </is>
       </c>
       <c r="N66" s="20" t="inlineStr">
@@ -10924,7 +10964,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Bourání otvorů pro nové dveře/okna</t>
+          <t>Bourání lehkých příček</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -10934,16 +10974,16 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="n">
-        <v>8</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H67" s="10" t="n"/>
       <c r="I67" s="10" t="n"/>
@@ -10962,12 +11002,12 @@
       </c>
       <c r="M67" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + statika — nové otvory s IPN160 překlady</t>
+          <t>TZ ARS dům §3 — lehké příčky bourány</t>
         </is>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O67" s="26" t="inlineStr">
@@ -10987,26 +11027,26 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Bourání obkladů v koupelnách</t>
+          <t>Bourání otvorů pro nové dveře/okna</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>781473810</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="n">
-        <v>60</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="n">
+        <v>8</v>
       </c>
       <c r="H68" s="10" t="n"/>
       <c r="I68" s="10" t="n"/>
@@ -11020,17 +11060,17 @@
       </c>
       <c r="L68" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — koupelny kompletně bourány</t>
+          <t>TZ ARS + statika — nové otvory s IPN160 překlady</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O68" s="26" t="inlineStr">
@@ -11050,17 +11090,17 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Bourání podlah 1.NP + 2.NP</t>
+          <t>Bourání obkladů v koupelnách</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>974031132</t>
+          <t>781473810</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -11069,7 +11109,7 @@
         </is>
       </c>
       <c r="G69" s="22" t="n">
-        <v>153.51</v>
+        <v>60</v>
       </c>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="10" t="n"/>
@@ -11083,12 +11123,12 @@
       </c>
       <c r="L69" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M69" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — podlahy 1.NP+2.NP sejmuty</t>
+          <t>TZ ARS dům §3 — koupelny kompletně bourány</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
@@ -11113,26 +11153,26 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Záklop + zásyp — demontáž</t>
+          <t>Bourání podlah 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>974041151</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G70" s="22" t="n">
-        <v>5</v>
+        <v>153.51</v>
       </c>
       <c r="H70" s="10" t="n"/>
       <c r="I70" s="10" t="n"/>
@@ -11151,7 +11191,7 @@
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — záklop+zásyp demontován; trámy zachovány</t>
+          <t>TZ ARS dům §3 — podlahy 1.NP+2.NP sejmuty</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -11176,26 +11216,26 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří</t>
+          <t>Záklop + zásyp — demontáž</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>974041151</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="n">
-        <v>25</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="n"/>
@@ -11214,12 +11254,12 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
+          <t>TZ ARS dům §3 — záklop+zásyp demontován; trámy zachovány</t>
         </is>
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O71" s="26" t="inlineStr">
@@ -11239,17 +11279,17 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů</t>
+          <t>Demontáž oken a dveří</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>968071120</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
@@ -11258,7 +11298,7 @@
         </is>
       </c>
       <c r="G72" s="23" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="10" t="n"/>
@@ -11277,12 +11317,12 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
+          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O72" s="26" t="inlineStr">
@@ -11302,26 +11342,26 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace</t>
+          <t>Demontáž zařizovacích předmětů</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="n">
-        <v>56.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="n">
+        <v>12</v>
       </c>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="n"/>
@@ -11331,7 +11371,7 @@
         </is>
       </c>
       <c r="K73" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
@@ -11340,12 +11380,12 @@
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů</t>
+          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O73" s="26" t="inlineStr">
@@ -11365,26 +11405,26 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken</t>
+          <t>Odvoz suti a likvidace</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="n">
-        <v>16</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="H74" s="10" t="n"/>
       <c r="I74" s="10" t="n"/>
@@ -11394,26 +11434,26 @@
         </is>
       </c>
       <c r="K74" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L74" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>TZ B m.10.e bilance odpadů</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="O74" s="25" t="inlineStr">
-        <is>
-          <t>OVĚŘENO ✓</t>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="O74" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11468,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních</t>
+          <t>Demontáž oken</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -11438,7 +11478,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
@@ -11447,7 +11487,7 @@
         </is>
       </c>
       <c r="G75" s="23" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H75" s="10" t="n"/>
       <c r="I75" s="10" t="n"/>
@@ -11466,7 +11506,7 @@
       </c>
       <c r="M75" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="N75" s="20" t="inlineStr">
@@ -11491,17 +11531,17 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní</t>
+          <t>Demontáž vstupních dveří venkovních</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
@@ -11510,7 +11550,7 @@
         </is>
       </c>
       <c r="G76" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="10" t="n"/>
@@ -11520,16 +11560,16 @@
         </is>
       </c>
       <c r="K76" s="24" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="L76" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M76" s="8" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
@@ -11537,9 +11577,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O76" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O76" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
     </row>
@@ -11554,26 +11594,26 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu</t>
+          <t>Demontáž vnitřních dveří vč. zárubní</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="n">
-        <v>0.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="n">
+        <v>15</v>
       </c>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="10" t="n"/>
@@ -11583,21 +11623,21 @@
         </is>
       </c>
       <c r="K77" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L77" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M77" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O77" s="26" t="inlineStr">
@@ -11617,17 +11657,17 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí</t>
+          <t>Bourání zdiva komínu</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
@@ -11636,7 +11676,7 @@
         </is>
       </c>
       <c r="G78" s="22" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="10" t="n"/>
@@ -11646,7 +11686,7 @@
         </is>
       </c>
       <c r="K78" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L78" s="20" t="inlineStr">
         <is>
@@ -11655,7 +11695,7 @@
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="N78" s="20" t="inlineStr">
@@ -11675,55 +11715,55 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu</t>
+          <t>Bourání venkovních konstrukcí</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>622401110</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G79" s="22" t="n">
-        <v>276.7</v>
+        <v>8</v>
       </c>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K79" s="24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L79" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M79" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O79" s="26" t="inlineStr">
@@ -11743,17 +11783,17 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm</t>
+          <t>Příprava podkladu</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>622221121</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -11776,12 +11816,12 @@
       </c>
       <c r="L80" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
@@ -11806,17 +11846,17 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>ETICS EPS 70F grey 160 mm</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221121</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -11825,7 +11865,7 @@
         </is>
       </c>
       <c r="G81" s="22" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
@@ -11844,12 +11884,12 @@
       </c>
       <c r="M81" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O81" s="26" t="inlineStr">
@@ -11869,26 +11909,26 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>ETICS sokl XPS</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622223111</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G82" s="22" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="n"/>
@@ -11898,21 +11938,21 @@
         </is>
       </c>
       <c r="K82" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O82" s="26" t="inlineStr">
@@ -11932,7 +11972,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -11942,16 +11982,16 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>82.2</v>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
@@ -11970,12 +12010,12 @@
       </c>
       <c r="M83" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O83" s="26" t="inlineStr">
@@ -11995,26 +12035,26 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>290.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="n"/>
@@ -12024,16 +12064,16 @@
         </is>
       </c>
       <c r="K84" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L84" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -12053,22 +12093,22 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
@@ -12077,17 +12117,17 @@
         </is>
       </c>
       <c r="G85" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>290.2</v>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K85" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
@@ -12096,12 +12136,12 @@
       </c>
       <c r="M85" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O85" s="26" t="inlineStr">
@@ -12121,26 +12161,26 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>712381111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G86" s="22" t="n">
-        <v>12</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="n"/>
@@ -12159,12 +12199,12 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O86" s="26" t="inlineStr">
@@ -12184,26 +12224,26 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
-        </is>
-      </c>
-      <c r="D87" s="27" t="inlineStr">
-        <is>
-          <t>711??? ?</t>
+          <t>Odvětrání radonu z podloží</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>40.5</v>
+        <v>12</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
@@ -12213,7 +12253,7 @@
         </is>
       </c>
       <c r="K87" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
@@ -12222,12 +12262,12 @@
       </c>
       <c r="M87" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O87" s="26" t="inlineStr">
@@ -12242,22 +12282,22 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>713121??? ?</t>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
@@ -12266,17 +12306,17 @@
         </is>
       </c>
       <c r="G88" s="22" t="n">
-        <v>177.5</v>
+        <v>40.5</v>
       </c>
       <c r="H88" s="10" t="n"/>
       <c r="I88" s="10" t="n"/>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K88" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L88" s="20" t="inlineStr">
         <is>
@@ -12285,7 +12325,7 @@
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -12310,7 +12350,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
@@ -12320,7 +12360,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -12329,7 +12369,7 @@
         </is>
       </c>
       <c r="G89" s="22" t="n">
-        <v>104.4</v>
+        <v>177.5</v>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
@@ -12339,7 +12379,7 @@
         </is>
       </c>
       <c r="K89" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L89" s="20" t="inlineStr">
         <is>
@@ -12348,12 +12388,12 @@
       </c>
       <c r="M89" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O89" s="26" t="inlineStr">
@@ -12368,41 +12408,41 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
-        </is>
-      </c>
-      <c r="D90" s="20" t="inlineStr">
-        <is>
-          <t>764312235</t>
+          <t>Kročejová EPS nad ocelobeton</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G90" s="22" t="n">
-        <v>69.5</v>
+        <v>104.4</v>
       </c>
       <c r="H90" s="10" t="n"/>
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K90" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L90" s="20" t="inlineStr">
         <is>
@@ -12411,12 +12451,12 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O90" s="26" t="inlineStr">
@@ -12436,17 +12476,17 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Oplechování krytiny</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -12455,7 +12495,7 @@
         </is>
       </c>
       <c r="G91" s="22" t="n">
-        <v>20.8</v>
+        <v>69.5</v>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
@@ -12465,7 +12505,7 @@
         </is>
       </c>
       <c r="K91" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
@@ -12474,12 +12514,12 @@
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O91" s="26" t="inlineStr">
@@ -12499,17 +12539,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -12518,7 +12558,7 @@
         </is>
       </c>
       <c r="G92" s="22" t="n">
-        <v>43.5</v>
+        <v>20.8</v>
       </c>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="10" t="n"/>
@@ -12528,7 +12568,7 @@
         </is>
       </c>
       <c r="K92" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L92" s="20" t="inlineStr">
         <is>
@@ -12537,7 +12577,7 @@
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -12562,17 +12602,17 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -12581,7 +12621,7 @@
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>26.1</v>
+        <v>43.5</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -12600,7 +12640,7 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
@@ -12620,50 +12660,50 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>766811111</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="n">
-        <v>16</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>26.1</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K94" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L94" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
@@ -12688,26 +12728,26 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D95" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Dřevěné stupně schodišť</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -12717,16 +12757,16 @@
         </is>
       </c>
       <c r="K95" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L95" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
@@ -12746,55 +12786,55 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
-        </is>
-      </c>
-      <c r="D96" s="20" t="inlineStr">
-        <is>
-          <t>766621011</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="n">
-        <v>2</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O96" s="26" t="inlineStr">
@@ -12814,7 +12854,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -12824,7 +12864,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
@@ -12833,7 +12873,7 @@
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
@@ -12847,12 +12887,12 @@
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
@@ -12877,7 +12917,7 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -12887,7 +12927,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
@@ -12896,7 +12936,7 @@
         </is>
       </c>
       <c r="G98" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -12915,7 +12955,7 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
@@ -12940,7 +12980,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -12950,7 +12990,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -12959,7 +12999,7 @@
         </is>
       </c>
       <c r="G99" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
@@ -12978,7 +13018,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
@@ -13003,7 +13043,7 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -13013,7 +13053,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -13022,7 +13062,7 @@
         </is>
       </c>
       <c r="G100" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
@@ -13041,7 +13081,7 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -13066,7 +13106,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -13076,7 +13116,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -13104,7 +13144,7 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
@@ -13129,7 +13169,7 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
@@ -13139,7 +13179,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
@@ -13148,7 +13188,7 @@
         </is>
       </c>
       <c r="G102" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
@@ -13167,7 +13207,7 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
@@ -13192,17 +13232,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -13211,17 +13251,17 @@
         </is>
       </c>
       <c r="G103" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -13230,7 +13270,7 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
@@ -13255,17 +13295,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -13274,17 +13314,17 @@
         </is>
       </c>
       <c r="G104" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K104" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L104" s="20" t="inlineStr">
         <is>
@@ -13293,12 +13333,12 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O104" s="26" t="inlineStr">
@@ -13318,17 +13358,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -13337,13 +13377,13 @@
         </is>
       </c>
       <c r="G105" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K105" s="24" t="n">
@@ -13356,12 +13396,12 @@
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O105" s="26" t="inlineStr">
@@ -13381,17 +13421,17 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
@@ -13400,17 +13440,17 @@
         </is>
       </c>
       <c r="G106" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
@@ -13419,12 +13459,12 @@
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O106" s="26" t="inlineStr">
@@ -13444,17 +13484,17 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
@@ -13463,17 +13503,17 @@
         </is>
       </c>
       <c r="G107" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
@@ -13482,7 +13522,7 @@
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
@@ -13502,55 +13542,55 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G108" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K108" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O108" s="26" t="inlineStr">
@@ -13570,7 +13610,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -13580,7 +13620,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -13608,12 +13648,12 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O109" s="26" t="inlineStr">
@@ -13633,26 +13673,26 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -13662,16 +13702,16 @@
         </is>
       </c>
       <c r="K110" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L110" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -13696,26 +13736,26 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>18</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -13734,7 +13774,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -13754,55 +13794,55 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G112" s="22" t="n">
-        <v>171.5</v>
+        <v>18</v>
       </c>
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="10" t="n"/>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K112" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L112" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O112" s="26" t="inlineStr">
@@ -13822,17 +13862,17 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -13841,13 +13881,13 @@
         </is>
       </c>
       <c r="G113" s="22" t="n">
-        <v>13.5</v>
+        <v>171.5</v>
       </c>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="n"/>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K113" s="24" t="n">
@@ -13855,12 +13895,12 @@
       </c>
       <c r="L113" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -13885,7 +13925,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -13895,7 +13935,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -13904,7 +13944,7 @@
         </is>
       </c>
       <c r="G114" s="22" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
@@ -13923,7 +13963,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -13948,17 +13988,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -13967,17 +14007,17 @@
         </is>
       </c>
       <c r="G115" s="22" t="n">
-        <v>25</v>
+        <v>32.4</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -13986,12 +14026,12 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O115" s="26" t="inlineStr">
@@ -14011,17 +14051,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -14030,17 +14070,17 @@
         </is>
       </c>
       <c r="G116" s="22" t="n">
-        <v>126.4</v>
+        <v>25</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="20" t="inlineStr">
         <is>
@@ -14049,12 +14089,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -14074,26 +14114,26 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G117" s="22" t="n">
-        <v>72.03</v>
+        <v>126.4</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
@@ -14112,12 +14152,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -14137,17 +14177,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -14156,13 +14196,13 @@
         </is>
       </c>
       <c r="G118" s="22" t="n">
-        <v>19.28</v>
+        <v>72.03</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
@@ -14175,7 +14215,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
@@ -14195,41 +14235,41 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G119" s="22" t="n">
-        <v>78.2</v>
+        <v>19.28</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
@@ -14238,12 +14278,12 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O119" s="26" t="inlineStr">
@@ -14263,7 +14303,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
@@ -14273,7 +14313,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
@@ -14282,7 +14322,7 @@
         </is>
       </c>
       <c r="G120" s="22" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="n"/>
@@ -14301,7 +14341,7 @@
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
@@ -14326,7 +14366,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -14336,7 +14376,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -14345,7 +14385,7 @@
         </is>
       </c>
       <c r="G121" s="22" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="10" t="n"/>
@@ -14364,7 +14404,7 @@
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
@@ -14389,7 +14429,7 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
@@ -14399,7 +14439,7 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
@@ -14408,7 +14448,7 @@
         </is>
       </c>
       <c r="G122" s="22" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -14427,7 +14467,7 @@
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -14452,17 +14492,17 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
@@ -14471,17 +14511,17 @@
         </is>
       </c>
       <c r="G123" s="22" t="n">
-        <v>59.5</v>
+        <v>179.1</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K123" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L123" s="20" t="inlineStr">
         <is>
@@ -14490,12 +14530,12 @@
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O123" s="26" t="inlineStr">
@@ -14515,7 +14555,7 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
@@ -14525,7 +14565,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
@@ -14534,7 +14574,7 @@
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
@@ -14553,7 +14593,7 @@
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
@@ -14578,7 +14618,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -14588,7 +14628,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -14597,7 +14637,7 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
@@ -14616,7 +14656,7 @@
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -14641,17 +14681,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -14660,17 +14700,17 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>13.4</v>
+        <v>64.5</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K126" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L126" s="20" t="inlineStr">
         <is>
@@ -14679,7 +14719,7 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
@@ -14704,7 +14744,7 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
@@ -14714,7 +14754,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -14723,7 +14763,7 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
@@ -14742,7 +14782,7 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
@@ -14767,7 +14807,7 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
@@ -14777,7 +14817,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
@@ -14786,7 +14826,7 @@
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
@@ -14805,7 +14845,7 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
@@ -14830,7 +14870,7 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
@@ -14840,7 +14880,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
@@ -14849,7 +14889,7 @@
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
@@ -14859,7 +14899,7 @@
         </is>
       </c>
       <c r="K129" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L129" s="20" t="inlineStr">
         <is>
@@ -14868,7 +14908,7 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
@@ -14893,17 +14933,17 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
@@ -14912,17 +14952,17 @@
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L130" s="20" t="inlineStr">
         <is>
@@ -14931,7 +14971,7 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
@@ -14956,7 +14996,7 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
@@ -14966,7 +15006,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
@@ -14975,7 +15015,7 @@
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>254.5</v>
+        <v>0</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
@@ -14985,7 +15025,7 @@
         </is>
       </c>
       <c r="K131" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L131" s="20" t="inlineStr">
         <is>
@@ -14994,7 +15034,7 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
@@ -15019,7 +15059,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -15029,7 +15069,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -15038,7 +15078,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>78.2</v>
+        <v>254.5</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -15057,7 +15097,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -15082,7 +15122,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -15092,7 +15132,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -15101,7 +15141,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>247.5</v>
+        <v>78.2</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -15120,7 +15160,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -15145,7 +15185,7 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
@@ -15155,7 +15195,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -15164,7 +15204,7 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>219.3</v>
+        <v>247.5</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
@@ -15183,7 +15223,7 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
@@ -15203,37 +15243,37 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="n">
-        <v>4</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>219.3</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K135" s="24" t="n">
@@ -15241,12 +15281,12 @@
       </c>
       <c r="L135" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
@@ -15271,17 +15311,17 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -15290,13 +15330,13 @@
         </is>
       </c>
       <c r="G136" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K136" s="24" t="n">
@@ -15304,12 +15344,12 @@
       </c>
       <c r="L136" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -15329,27 +15369,27 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G137" s="23" t="n">
@@ -15359,7 +15399,7 @@
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K137" s="24" t="n">
@@ -15372,12 +15412,12 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O137" s="26" t="inlineStr">
@@ -15397,26 +15437,26 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G138" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
@@ -15435,7 +15475,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -15460,26 +15500,26 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G139" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -15489,7 +15529,7 @@
         </is>
       </c>
       <c r="K139" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L139" s="20" t="inlineStr">
         <is>
@@ -15498,7 +15538,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -15523,26 +15563,26 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G140" s="23" t="n">
-        <v>70</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G140" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -15561,7 +15601,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -15586,17 +15626,17 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -15605,7 +15645,7 @@
         </is>
       </c>
       <c r="G141" s="23" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
@@ -15624,7 +15664,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -15649,26 +15689,26 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G142" s="23" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
@@ -15678,7 +15718,7 @@
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -15687,7 +15727,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -15712,17 +15752,17 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -15737,11 +15777,11 @@
       <c r="I143" s="10" t="n"/>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K143" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L143" s="20" t="inlineStr">
         <is>
@@ -15750,12 +15790,12 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O143" s="26" t="inlineStr">
@@ -15770,22 +15810,22 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -15800,25 +15840,25 @@
       <c r="I144" s="10" t="n"/>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K144" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L144" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O144" s="26" t="inlineStr">
@@ -15838,26 +15878,26 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G145" s="22" t="n">
-        <v>80</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -15867,7 +15907,7 @@
         </is>
       </c>
       <c r="K145" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L145" s="20" t="inlineStr">
         <is>
@@ -15876,7 +15916,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -15901,17 +15941,17 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
@@ -15920,7 +15960,7 @@
         </is>
       </c>
       <c r="G146" s="22" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
@@ -15934,12 +15974,12 @@
       </c>
       <c r="L146" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -15964,26 +16004,26 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G147" s="22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
@@ -16002,7 +16042,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -16027,26 +16067,26 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G148" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G148" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H148" s="10" t="n"/>
       <c r="I148" s="10" t="n"/>
@@ -16056,7 +16096,7 @@
         </is>
       </c>
       <c r="K148" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
@@ -16065,12 +16105,12 @@
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O148" s="26" t="inlineStr">
@@ -16090,17 +16130,17 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
@@ -16153,17 +16193,17 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
@@ -16216,26 +16256,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G151" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -16245,7 +16285,7 @@
         </is>
       </c>
       <c r="K151" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L151" s="20" t="inlineStr">
         <is>
@@ -16254,12 +16294,12 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O151" s="26" t="inlineStr">
@@ -16279,26 +16319,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -16308,7 +16348,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -16317,12 +16357,12 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O152" s="26" t="inlineStr">
@@ -16342,17 +16382,17 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
@@ -16405,17 +16445,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -16468,26 +16508,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G155" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -16497,7 +16537,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -16506,12 +16546,12 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O155" s="26" t="inlineStr">
@@ -16531,26 +16571,26 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G156" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G156" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H156" s="10" t="n"/>
       <c r="I156" s="10" t="n"/>
@@ -16560,7 +16600,7 @@
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -16569,12 +16609,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -16594,17 +16634,17 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -16657,17 +16697,17 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
@@ -16720,17 +16760,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -16739,7 +16779,7 @@
         </is>
       </c>
       <c r="G159" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -16749,7 +16789,7 @@
         </is>
       </c>
       <c r="K159" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
@@ -16758,12 +16798,12 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O159" s="26" t="inlineStr">
@@ -16783,17 +16823,17 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
@@ -16802,7 +16842,7 @@
         </is>
       </c>
       <c r="G160" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -16812,7 +16852,7 @@
         </is>
       </c>
       <c r="K160" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L160" s="20" t="inlineStr">
         <is>
@@ -16821,7 +16861,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -16846,17 +16886,17 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
@@ -16865,17 +16905,17 @@
         </is>
       </c>
       <c r="G161" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -16884,7 +16924,7 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
@@ -16909,17 +16949,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -16934,7 +16974,7 @@
       <c r="I162" s="10" t="n"/>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K162" s="24" t="n">
@@ -16947,7 +16987,7 @@
       </c>
       <c r="M162" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N162" s="20" t="inlineStr">
@@ -16967,22 +17007,22 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -16997,7 +17037,7 @@
       <c r="I163" s="10" t="n"/>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K163" s="24" t="n">
@@ -17010,7 +17050,7 @@
       </c>
       <c r="M163" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N163" s="20" t="inlineStr">
@@ -17035,22 +17075,22 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G164" s="23" t="n">
@@ -17064,7 +17104,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -17073,12 +17113,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -17098,22 +17138,22 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G165" s="23" t="n">
@@ -17127,7 +17167,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -17136,12 +17176,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -17161,17 +17201,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -17199,7 +17239,7 @@
       </c>
       <c r="M166" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N166" s="20" t="inlineStr">
@@ -17224,17 +17264,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -17249,7 +17289,7 @@
       <c r="I167" s="10" t="n"/>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K167" s="24" t="n">
@@ -17262,7 +17302,7 @@
       </c>
       <c r="M167" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N167" s="20" t="inlineStr">
@@ -17287,17 +17327,17 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
@@ -17306,7 +17346,7 @@
         </is>
       </c>
       <c r="G168" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -17316,7 +17356,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -17325,7 +17365,7 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
@@ -17350,36 +17390,36 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G169" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
       <c r="J169" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -17388,7 +17428,7 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
@@ -17413,36 +17453,36 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G170" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H170" s="10" t="n"/>
       <c r="I170" s="10" t="n"/>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K170" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L170" s="20" t="inlineStr">
         <is>
@@ -17451,7 +17491,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N170" s="20" t="inlineStr">
@@ -17471,41 +17511,41 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G171" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G171" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H171" s="10" t="n"/>
       <c r="I171" s="10" t="n"/>
       <c r="J171" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K171" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L171" s="20" t="inlineStr">
         <is>
@@ -17514,12 +17554,12 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N171" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O171" s="26" t="inlineStr">
@@ -17534,22 +17574,22 @@
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -17577,12 +17617,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -17597,41 +17637,41 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -17640,12 +17680,12 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O173" s="26" t="inlineStr">
@@ -17665,36 +17705,36 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -17703,12 +17743,12 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O174" s="26" t="inlineStr">
@@ -17728,36 +17768,36 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G175" s="22" t="n">
-        <v>56.9</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G175" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H175" s="10" t="n"/>
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L175" s="20" t="inlineStr">
         <is>
@@ -17766,12 +17806,12 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O175" s="26" t="inlineStr">
@@ -17786,41 +17826,41 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G176" s="23" t="n">
-        <v>2</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G176" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H176" s="10" t="n"/>
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L176" s="20" t="inlineStr">
         <is>
@@ -17829,12 +17869,12 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O176" s="26" t="inlineStr">
@@ -17849,37 +17889,37 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H177" s="10" t="n"/>
       <c r="I177" s="10" t="n"/>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K177" s="24" t="n">
@@ -17892,7 +17932,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
@@ -17912,31 +17952,31 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G178" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G178" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H178" s="10" t="n"/>
       <c r="I178" s="10" t="n"/>
@@ -17946,7 +17986,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -17955,7 +17995,7 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
@@ -17975,31 +18015,31 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G179" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G179" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H179" s="10" t="n"/>
       <c r="I179" s="10" t="n"/>
@@ -18009,7 +18049,7 @@
         </is>
       </c>
       <c r="K179" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L179" s="20" t="inlineStr">
         <is>
@@ -18018,12 +18058,12 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O179" s="26" t="inlineStr">
@@ -18043,22 +18083,22 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G180" s="23" t="n">
@@ -18072,7 +18112,7 @@
         </is>
       </c>
       <c r="K180" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L180" s="20" t="inlineStr">
         <is>
@@ -18081,7 +18121,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -18101,22 +18141,22 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -18131,11 +18171,11 @@
       <c r="I181" s="10" t="n"/>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -18144,7 +18184,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -18169,17 +18209,17 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
@@ -18194,7 +18234,7 @@
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
@@ -18207,7 +18247,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -18227,41 +18267,41 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -18270,12 +18310,12 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O183" s="26" t="inlineStr">
@@ -18290,41 +18330,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G184" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -18333,7 +18373,7 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
@@ -18353,41 +18393,41 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H185" s="10" t="n"/>
       <c r="I185" s="10" t="n"/>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K185" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L185" s="20" t="inlineStr">
         <is>
@@ -18396,12 +18436,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -18421,22 +18461,22 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
@@ -18459,7 +18499,7 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
@@ -18484,26 +18524,26 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
@@ -18522,7 +18562,7 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
@@ -18547,17 +18587,17 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
@@ -18576,32 +18616,95 @@
         </is>
       </c>
       <c r="K188" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L188" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M188" s="8" t="inlineStr">
+        <is>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+        </is>
+      </c>
+      <c r="N188" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O188" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="20" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště</t>
+        </is>
+      </c>
+      <c r="D189" s="20" t="inlineStr">
+        <is>
+          <t>012103101</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+        </is>
+      </c>
+      <c r="F189" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" s="10" t="n"/>
+      <c r="I189" s="10" t="n"/>
+      <c r="J189" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K189" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="L188" s="20" t="inlineStr">
+      <c r="L189" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M188" s="8" t="inlineStr">
+      <c r="M189" s="8" t="inlineStr">
         <is>
           <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
-      <c r="N188" s="20" t="inlineStr">
+      <c r="N189" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O188" s="26" t="inlineStr">
+      <c r="O189" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O188"/>
-  <conditionalFormatting sqref="K2:K188">
+  <autoFilter ref="A1:O189"/>
+  <conditionalFormatting sqref="K2:K189">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -24218,7 +24218,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP…</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň pr…</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -18,11 +18,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_F_URS_Verification_Trail" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -969,11 +969,11 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>GROUP BY kapitola per objekt (24 souhrnných řádků). Pro orientační cenovku.</t>
+          <t>GROUP BY kapitola per objekt (25 souhrnných řádků). Pro orientační cenovku.</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="n"/>
@@ -987,11 +987,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 130 řádků.</t>
+          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (200 dum + 28 sklad = 228 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (203 dum + 31 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>228 (200 dum + 28 sklad)</t>
+          <t>234 (203 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 118 | PSV 54 | TZB 34 | VRN 22</t>
+          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 72 | 0.70: 2 | 0.60: 2 | 0.50: 4 | 0.00: 4</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 72 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.5 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 150 needs_production_lookup (65.8 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 156 needs_production_lookup (66.7 %)</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>28 items (viz Otazky_pro_Karla docx)</t>
+          <t>29 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1160,8 +1160,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-228 položek celkem (200 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 72×0.75 · 2×0.70 · 2×0.60 · 4×0.50 · 4×0.00.
+234 položek celkem (203 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 72×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1476,11 +1476,11 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; Zásuvky a vypínače; … (+3 dalších)</t>
+          <t>Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; Zásuvky a vypínače; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
@@ -1496,16 +1496,16 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; Podlahový EPS 150; … (+1 dalších)</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
@@ -1521,16 +1521,16 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; Sanitární keramika koupelna 1.05 (1.NP); … (+15 dalších)</t>
+          <t>HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; Podlahový EPS 150; … (+1 dalších)</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; Krb na tuhá paliva 3.NP; … (+4 dalších)</t>
+          <t>Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; Sanitární keramika koupelna 1.05 (1.NP); … (+15 dalších)</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
@@ -1571,16 +1571,16 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); Plastové okno trojsklo — 'okno 3.NP' (ulice); … (+18 dalších)</t>
+          <t>Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; Krb na tuhá paliva 3.NP; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
@@ -1596,16 +1596,16 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; Nášlap biodeska 3.NP spací patro; … (+3 dalších)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); Plastové okno trojsklo — 'okno 3.NP' (ulice); … (+18 dalších)</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n"/>
@@ -1621,16 +1621,16 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; Omítka jádrová + štuk 3.NP; … (+12 dalších)</t>
+          <t>Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; Nášlap biodeska 3.NP spací patro; … (+3 dalších)</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
@@ -1646,16 +1646,16 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; Omítka jádrová + štuk 3.NP; … (+12 dalších)</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="n"/>
@@ -1671,16 +1671,16 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; Kontejnery suti tříděné; … (+14 dalších)</t>
+          <t>Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
@@ -1690,8 +1690,33 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; Kontejnery suti tříděné; … (+14 dalších)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>agregát — detail viz List B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1862,11 +1887,11 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Sklad mezipodesta schodiště prefa; Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -1887,11 +1912,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -1937,11 +1962,11 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; Podíl na obecných VRN dům</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; Podíl na obecných VRN dům; … (+1 dalších)</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
@@ -1963,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6751,34 +6776,32 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="n"/>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6793,12 +6816,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -6833,12 +6856,12 @@
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -6868,17 +6891,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -6913,12 +6936,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -6953,12 +6976,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -6993,12 +7016,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -7033,12 +7056,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -7073,12 +7096,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -7113,12 +7136,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -7153,12 +7176,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -7193,12 +7216,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -7222,8 +7245,88 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7234,7 +7337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O201"/>
+  <dimension ref="A1:O204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16652,27 +16755,27 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
@@ -16682,11 +16785,11 @@
       <c r="I150" s="10" t="n"/>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K150" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L150" s="20" t="inlineStr">
         <is>
@@ -16695,12 +16798,12 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O150" s="26" t="inlineStr">
@@ -16720,26 +16823,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G151" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -16758,7 +16861,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -16783,26 +16886,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G152" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -16812,7 +16915,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -16821,7 +16924,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -16846,26 +16949,26 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="n">
-        <v>70</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -16884,7 +16987,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -16909,17 +17012,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -16928,7 +17031,7 @@
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -16947,7 +17050,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -16972,26 +17075,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -17001,7 +17104,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -17010,7 +17113,7 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
@@ -17035,17 +17138,17 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -17060,11 +17163,11 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -17073,12 +17176,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -17093,22 +17196,22 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -17123,25 +17226,25 @@
       <c r="I157" s="10" t="n"/>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O157" s="26" t="inlineStr">
@@ -17161,26 +17264,26 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G158" s="22" t="n">
-        <v>80</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G158" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -17190,7 +17293,7 @@
         </is>
       </c>
       <c r="K158" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
@@ -17199,7 +17302,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -17224,17 +17327,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -17243,7 +17346,7 @@
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -17257,12 +17360,12 @@
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -17287,26 +17390,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G160" s="22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -17325,7 +17428,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -17350,26 +17453,26 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G161" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G161" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
@@ -17379,7 +17482,7 @@
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -17388,12 +17491,12 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O161" s="26" t="inlineStr">
@@ -17413,17 +17516,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -17476,17 +17579,17 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -17539,26 +17642,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G164" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -17568,7 +17671,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -17577,12 +17680,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -17602,26 +17705,26 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G165" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G165" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H165" s="10" t="n"/>
       <c r="I165" s="10" t="n"/>
@@ -17631,7 +17734,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -17640,12 +17743,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -17665,17 +17768,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -17728,17 +17831,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -17791,26 +17894,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G168" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -17820,7 +17923,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -17829,12 +17932,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -17854,26 +17957,26 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G169" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G169" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
@@ -17883,7 +17986,7 @@
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -17892,12 +17995,12 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O169" s="26" t="inlineStr">
@@ -17917,17 +18020,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -17980,17 +18083,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -18043,17 +18146,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -18062,7 +18165,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -18072,7 +18175,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -18081,12 +18184,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -18106,17 +18209,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -18125,7 +18228,7 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
@@ -18135,7 +18238,7 @@
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -18144,7 +18247,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -18169,17 +18272,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -18188,17 +18291,17 @@
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -18207,7 +18310,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -18232,17 +18335,17 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -18257,7 +18360,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -18270,7 +18373,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -18290,22 +18393,22 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -18320,7 +18423,7 @@
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
@@ -18333,7 +18436,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
@@ -18358,22 +18461,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -18387,7 +18490,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -18396,12 +18499,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -18421,22 +18524,22 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G178" s="23" t="n">
@@ -18450,7 +18553,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -18459,12 +18562,12 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O178" s="26" t="inlineStr">
@@ -18484,17 +18587,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -18522,7 +18625,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -18547,17 +18650,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -18572,7 +18675,7 @@
       <c r="I180" s="10" t="n"/>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K180" s="24" t="n">
@@ -18585,7 +18688,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -18610,17 +18713,17 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -18629,7 +18732,7 @@
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
@@ -18639,7 +18742,7 @@
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -18648,7 +18751,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -18673,36 +18776,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G182" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -18711,7 +18814,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -18736,36 +18839,36 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -18774,7 +18877,7 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
@@ -18794,41 +18897,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G184" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -18837,12 +18940,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -18857,22 +18960,22 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
@@ -18900,12 +19003,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -18920,41 +19023,41 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -18963,12 +19066,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -18988,36 +19091,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -19026,12 +19129,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -19051,36 +19154,36 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G188" s="22" t="n">
-        <v>56.9</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G188" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -19089,12 +19192,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -19109,41 +19212,41 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="n">
-        <v>2</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G189" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L189" s="20" t="inlineStr">
         <is>
@@ -19152,12 +19255,12 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O189" s="26" t="inlineStr">
@@ -19172,37 +19275,37 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G190" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K190" s="24" t="n">
@@ -19215,7 +19318,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -19235,31 +19338,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G191" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -19269,7 +19372,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -19278,7 +19381,7 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
@@ -19298,31 +19401,31 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G192" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G192" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H192" s="10" t="n"/>
       <c r="I192" s="10" t="n"/>
@@ -19332,7 +19435,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -19341,12 +19444,12 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O192" s="26" t="inlineStr">
@@ -19366,22 +19469,22 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
@@ -19395,7 +19498,7 @@
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -19404,7 +19507,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -19424,22 +19527,22 @@
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -19454,11 +19557,11 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L194" s="20" t="inlineStr">
         <is>
@@ -19467,7 +19570,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -19492,17 +19595,17 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
@@ -19517,7 +19620,7 @@
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
@@ -19530,7 +19633,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
@@ -19550,41 +19653,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G196" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G196" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -19593,12 +19696,12 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O196" s="26" t="inlineStr">
@@ -19613,41 +19716,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G197" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G197" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -19656,7 +19759,7 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
@@ -19676,41 +19779,41 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H198" s="10" t="n"/>
       <c r="I198" s="10" t="n"/>
       <c r="J198" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K198" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L198" s="20" t="inlineStr">
         <is>
@@ -19719,12 +19822,12 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O198" s="26" t="inlineStr">
@@ -19744,22 +19847,22 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
@@ -19782,7 +19885,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -19807,26 +19910,26 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G200" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H200" s="10" t="n"/>
       <c r="I200" s="10" t="n"/>
@@ -19845,7 +19948,7 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
@@ -19870,17 +19973,17 @@
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
@@ -19899,32 +20002,221 @@
         </is>
       </c>
       <c r="K201" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L201" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M201" s="8" t="inlineStr">
+        <is>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+        </is>
+      </c>
+      <c r="N201" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O201" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="20" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště</t>
+        </is>
+      </c>
+      <c r="D202" s="20" t="inlineStr">
+        <is>
+          <t>012103101</t>
+        </is>
+      </c>
+      <c r="E202" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+        </is>
+      </c>
+      <c r="F202" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G202" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" s="10" t="n"/>
+      <c r="I202" s="10" t="n"/>
+      <c r="J202" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K202" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="L201" s="20" t="inlineStr">
+      <c r="L202" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M201" s="8" t="inlineStr">
+      <c r="M202" s="8" t="inlineStr">
         <is>
           <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
-      <c r="N201" s="20" t="inlineStr">
+      <c r="N202" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O201" s="26" t="inlineStr">
+      <c r="O202" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="20" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+        </is>
+      </c>
+      <c r="D203" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+        </is>
+      </c>
+      <c r="F203" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G203" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" s="10" t="n"/>
+      <c r="I203" s="10" t="n"/>
+      <c r="J203" s="8" t="inlineStr">
+        <is>
+          <t>elektrikar</t>
+        </is>
+      </c>
+      <c r="K203" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L203" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M203" s="8" t="inlineStr">
+        <is>
+          <t>PBŘ D.3 §16.05/16.06</t>
+        </is>
+      </c>
+      <c r="N203" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O203" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="20" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>M-24 VZT</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>Lokální odtah digestoří kuchyní</t>
+        </is>
+      </c>
+      <c r="D204" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="inlineStr">
+        <is>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
+        </is>
+      </c>
+      <c r="F204" s="20" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G204" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H204" s="10" t="n"/>
+      <c r="I204" s="10" t="n"/>
+      <c r="J204" s="8" t="inlineStr">
+        <is>
+          <t>vzduchotechnik</t>
+        </is>
+      </c>
+      <c r="K204" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L204" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M204" s="8" t="inlineStr">
+        <is>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
+        </is>
+      </c>
+      <c r="N204" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O204" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O201"/>
-  <conditionalFormatting sqref="K2:K201">
+  <autoFilter ref="A1:O204"/>
+  <conditionalFormatting sqref="K2:K204">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
@@ -19942,12 +20234,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -21430,41 +21722,39 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="n"/>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
@@ -21473,7 +21763,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -21493,50 +21783,50 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D25" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="n">
-        <v>17.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -21544,9 +21834,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O25" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O25" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -21556,27 +21846,27 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G26" s="23" t="n">
@@ -21586,11 +21876,11 @@
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
@@ -21599,7 +21889,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -21619,50 +21909,50 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>8</v>
+        <v>17.6</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -21670,9 +21960,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O27" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O27" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
       </c>
     </row>
@@ -21682,22 +21972,22 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -21712,11 +22002,11 @@
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
@@ -21725,7 +22015,7 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -21745,66 +22035,255 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
+          <t>bourani_demolice</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+        </is>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O29" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+        </is>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N31" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O31" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
           <t>VRN_management</t>
         </is>
       </c>
-      <c r="K29" s="24" t="n">
+      <c r="K32" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="L29" s="20" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
         </is>
       </c>
-      <c r="N29" s="20" t="inlineStr">
+      <c r="N32" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O29" s="26" t="inlineStr">
+      <c r="O32" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
-  <conditionalFormatting sqref="K2:K29">
+  <autoFilter ref="A1:O32"/>
+  <conditionalFormatting sqref="K2:K32">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -20,8 +20,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$203</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -987,11 +987,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
+          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 131 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (203 dum + 31 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (202 dum + 31 sklad = 233 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>234 (203 dum + 31 sklad)</t>
+          <t>233 (202 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 118 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 72 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 156 needs_production_lookup (66.7 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 155 needs_production_lookup (66.5 %)</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>29 items (viz Otazky_pro_Karla docx)</t>
+          <t>30 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1160,8 +1160,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-234 položek celkem (203 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 72×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+233 položek celkem (202 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1426,11 +1426,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu; Bourání plechové střešní krytiny; Bourání nadezdívek nad stropem 2.NP; Bourání trámového stropu 2.NP/podkroví; … (+14 dalších)</t>
+          <t>Bourání kompletního stávajícího krovu; Bourání plechové střešní krytiny; Bourání nadezdívek nad stropem 2.NP; Bourání trámového stropu 2.NP/podkroví; … (+13 dalších)</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -1988,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří — Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž zařizovacích předmětů — Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="F90" s="23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G90" s="10" t="n"/>
       <c r="H90" s="10" t="n"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968071120</t>
+          <t>URS-prop 725900001</t>
         </is>
       </c>
     </row>
@@ -5631,16 +5631,16 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů — Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Odvoz suti a likvidace — Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="n">
-        <v>12</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 725900001</t>
+          <t>URS-prop 997013501</t>
         </is>
       </c>
     </row>
@@ -5666,32 +5666,32 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace — Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Příprava podkladu — Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F92" s="22" t="n">
-        <v>56.5</v>
+        <v>276.7</v>
       </c>
       <c r="G92" s="10" t="n"/>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 997013501</t>
+          <t>URS-prop 622401110</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu — Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>ETICS EPS 70F grey 160 mm — ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622401110</t>
+          <t>URS-prop 622221121</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm — ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="F94" s="22" t="n">
-        <v>276.7</v>
+        <v>13.5</v>
       </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221121</t>
+          <t>URS-prop 622223111</t>
         </is>
       </c>
     </row>
@@ -5791,16 +5791,16 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="F95" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622223111</t>
+          <t>URS-prop 622221221</t>
         </is>
       </c>
     </row>
@@ -5831,16 +5831,16 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="F96" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
@@ -5871,16 +5871,16 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="F97" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>290.2</v>
       </c>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221221</t>
+          <t>URS-prop 622521111</t>
         </is>
       </c>
     </row>
@@ -5906,32 +5906,32 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>290.2</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622521111</t>
+          <t>URS-prop 978013181</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="F99" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="F100" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 978013181</t>
+          <t>URS-prop 968072456</t>
         </is>
       </c>
     </row>
@@ -6031,16 +6031,16 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F101" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968072456</t>
+          <t>URS-prop 962024141</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 962024141</t>
+          <t>URS-prop 961044111</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F103" s="22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 961044111</t>
+          <t>URS-prop 877315111</t>
         </is>
       </c>
     </row>
@@ -6141,37 +6141,37 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
+          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F104" s="22" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 877315111</t>
+          <t>URS-prop 121301101</t>
         </is>
       </c>
     </row>
@@ -6181,37 +6181,37 @@
       </c>
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>5.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="n">
+        <v>13</v>
       </c>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 121301101</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
@@ -6240,18 +6240,18 @@
         </is>
       </c>
       <c r="F106" s="23" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -6266,32 +6266,32 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
+          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F107" s="23" t="n">
-        <v>50</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>59.5</v>
       </c>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>tesar</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 762085112</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
+          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
+          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="F109" s="22" t="n">
-        <v>59.5</v>
+        <v>104.4</v>
       </c>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713121</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
+          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -6399,19 +6399,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F110" s="22" t="n">
-        <v>104.4</v>
-      </c>
+      <c r="F110" s="22" t="n"/>
       <c r="G110" s="10" t="n"/>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713121</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6429,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
+          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -6444,12 +6442,12 @@
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6467,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
+          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -6482,12 +6480,12 @@
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6505,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
+          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -6540,12 +6538,12 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
+          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -6553,12 +6551,14 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F114" s="22" t="n"/>
+      <c r="F114" s="22" t="n">
+        <v>23</v>
+      </c>
       <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -6598,7 +6598,7 @@
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -6638,7 +6638,7 @@
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -6672,13 +6672,13 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>23</v>
+        <v>140.94</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>pokryvac</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="F118" s="22" t="n">
-        <v>140.94</v>
+        <v>23</v>
       </c>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>pokryvac</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -6733,17 +6733,17 @@
       </c>
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
@@ -6751,14 +6751,12 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F119" s="22" t="n">
-        <v>23</v>
-      </c>
+      <c r="F119" s="22" t="n"/>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
@@ -6776,32 +6774,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+      <c r="C120" s="21" t="inlineStr">
+        <is>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F120" s="22" t="n"/>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>agregát</t>
         </is>
       </c>
     </row>
@@ -6816,12 +6816,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -6891,17 +6891,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -7256,12 +7256,12 @@
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
@@ -7285,48 +7285,8 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="20" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="20" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C133" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="D133" s="8" t="inlineStr">
-        <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
-        </is>
-      </c>
-      <c r="E133" s="20" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="10" t="n"/>
-      <c r="H133" s="10" t="n"/>
-      <c r="I133" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J133" s="8" t="inlineStr">
-        <is>
-          <t>agregát</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J133"/>
+  <autoFilter ref="A1:J132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7337,7 +7297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:O203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12350,17 +12310,17 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří</t>
+          <t>Demontáž zařizovacích předmětů</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -12369,7 +12329,7 @@
         </is>
       </c>
       <c r="G80" s="23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H80" s="10" t="n"/>
       <c r="I80" s="10" t="n"/>
@@ -12388,12 +12348,12 @@
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
+          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O80" s="26" t="inlineStr">
@@ -12413,26 +12373,26 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů</t>
+          <t>Odvoz suti a likvidace</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="n">
-        <v>12</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
@@ -12442,7 +12402,7 @@
         </is>
       </c>
       <c r="K81" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L81" s="20" t="inlineStr">
         <is>
@@ -12451,12 +12411,12 @@
       </c>
       <c r="M81" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
+          <t>TZ B m.10.e bilance odpadů</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O81" s="26" t="inlineStr">
@@ -12476,26 +12436,26 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace</t>
+          <t>Demontáž oken</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="n">
-        <v>56.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="n"/>
@@ -12505,26 +12465,26 @@
         </is>
       </c>
       <c r="K82" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
-        </is>
-      </c>
-      <c r="O82" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="O82" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12499,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken</t>
+          <t>Demontáž vstupních dveří venkovních</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -12549,7 +12509,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
@@ -12558,7 +12518,7 @@
         </is>
       </c>
       <c r="G83" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
@@ -12577,7 +12537,7 @@
       </c>
       <c r="M83" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
@@ -12602,17 +12562,17 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních</t>
+          <t>Demontáž vnitřních dveří vč. zárubní</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
@@ -12621,7 +12581,7 @@
         </is>
       </c>
       <c r="G84" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="n"/>
@@ -12631,16 +12591,16 @@
         </is>
       </c>
       <c r="K84" s="24" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="L84" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -12648,9 +12608,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O84" s="25" t="inlineStr">
-        <is>
-          <t>OVĚŘENO ✓</t>
+      <c r="O84" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -12665,26 +12625,26 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní</t>
+          <t>Bourání zdiva komínu</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
@@ -12694,21 +12654,21 @@
         </is>
       </c>
       <c r="K85" s="24" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M85" s="8" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O85" s="26" t="inlineStr">
@@ -12728,17 +12688,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu</t>
+          <t>Bourání venkovních konstrukcí</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
@@ -12747,7 +12707,7 @@
         </is>
       </c>
       <c r="G86" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="n"/>
@@ -12757,7 +12717,7 @@
         </is>
       </c>
       <c r="K86" s="24" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="L86" s="20" t="inlineStr">
         <is>
@@ -12766,7 +12726,7 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
@@ -12791,50 +12751,50 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající)</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="K87" s="24" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M87" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O87" s="26" t="inlineStr">
@@ -12849,12 +12809,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající)</t>
+          <t>Sokl suterénu — sanační zateplení (S03)</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -12864,7 +12824,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
@@ -12879,7 +12839,7 @@
       <c r="I88" s="10" t="n"/>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="K88" s="24" t="n">
@@ -12892,7 +12852,7 @@
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
+          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -12917,7 +12877,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03)</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a)</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -12927,7 +12887,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -12942,7 +12902,7 @@
       <c r="I89" s="10" t="n"/>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K89" s="24" t="n">
@@ -12955,7 +12915,7 @@
       </c>
       <c r="M89" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
+          <t>Řez A-A/C-C sokl + obvod ETICS</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
@@ -12980,7 +12940,7 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a)</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b)</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -12990,7 +12950,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
@@ -13005,7 +12965,7 @@
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K90" s="24" t="n">
@@ -13018,7 +12978,7 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A/C-C sokl + obvod ETICS</t>
+          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
         </is>
       </c>
       <c r="N90" s="20" t="inlineStr">
@@ -13038,22 +12998,22 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b)</t>
+          <t>Příprava podkladu</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -13062,17 +13022,17 @@
         </is>
       </c>
       <c r="G91" s="22" t="n">
-        <v>23</v>
+        <v>276.7</v>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K91" s="24" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
@@ -13081,12 +13041,12 @@
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
+          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O91" s="26" t="inlineStr">
@@ -13106,17 +13066,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu</t>
+          <t>ETICS EPS 70F grey 160 mm</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>622401110</t>
+          <t>622221121</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -13139,12 +13099,12 @@
       </c>
       <c r="L92" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -13169,17 +13129,17 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm</t>
+          <t>ETICS sokl XPS</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>622221121</t>
+          <t>622223111</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -13188,7 +13148,7 @@
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>276.7</v>
+        <v>13.5</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -13207,12 +13167,12 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O93" s="26" t="inlineStr">
@@ -13232,26 +13192,26 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G94" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
@@ -13261,21 +13221,21 @@
         </is>
       </c>
       <c r="K94" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L94" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O94" s="26" t="inlineStr">
@@ -13295,7 +13255,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -13305,16 +13265,16 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -13333,12 +13293,12 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O95" s="26" t="inlineStr">
@@ -13358,26 +13318,26 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>290.2</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
@@ -13387,16 +13347,16 @@
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
@@ -13416,22 +13376,22 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
@@ -13440,17 +13400,17 @@
         </is>
       </c>
       <c r="G97" s="22" t="n">
-        <v>290.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K97" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
@@ -13459,12 +13419,12 @@
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O97" s="26" t="inlineStr">
@@ -13484,26 +13444,26 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Odvětrání radonu z podloží</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G98" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>12</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -13522,12 +13482,12 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O98" s="26" t="inlineStr">
@@ -13547,26 +13507,26 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
-        </is>
-      </c>
-      <c r="D99" s="20" t="inlineStr">
-        <is>
-          <t>712381111</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+        </is>
+      </c>
+      <c r="D99" s="27" t="inlineStr">
+        <is>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G99" s="22" t="n">
-        <v>12</v>
+        <v>40.5</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
@@ -13576,7 +13536,7 @@
         </is>
       </c>
       <c r="K99" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
@@ -13585,12 +13545,12 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O99" s="26" t="inlineStr">
@@ -13605,22 +13565,22 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>711??? ?</t>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -13629,17 +13589,17 @@
         </is>
       </c>
       <c r="G100" s="22" t="n">
-        <v>40.5</v>
+        <v>177.5</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K100" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L100" s="20" t="inlineStr">
         <is>
@@ -13648,7 +13608,7 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -13673,7 +13633,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>Kročejová EPS nad ocelobeton</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
@@ -13683,7 +13643,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -13692,7 +13652,7 @@
         </is>
       </c>
       <c r="G101" s="22" t="n">
-        <v>177.5</v>
+        <v>104.4</v>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
@@ -13702,7 +13662,7 @@
         </is>
       </c>
       <c r="K101" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L101" s="20" t="inlineStr">
         <is>
@@ -13711,12 +13671,12 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O101" s="26" t="inlineStr">
@@ -13731,41 +13691,41 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
-        </is>
-      </c>
-      <c r="D102" s="27" t="inlineStr">
-        <is>
-          <t>713121??? ?</t>
+          <t>Oplechování krytiny</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G102" s="22" t="n">
-        <v>104.4</v>
+        <v>69.5</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K102" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L102" s="20" t="inlineStr">
         <is>
@@ -13774,12 +13734,12 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O102" s="26" t="inlineStr">
@@ -13799,17 +13759,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -13818,7 +13778,7 @@
         </is>
       </c>
       <c r="G103" s="22" t="n">
-        <v>69.5</v>
+        <v>20.8</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
@@ -13828,7 +13788,7 @@
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -13837,12 +13797,12 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O103" s="26" t="inlineStr">
@@ -13862,17 +13822,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -13881,7 +13841,7 @@
         </is>
       </c>
       <c r="G104" s="22" t="n">
-        <v>20.8</v>
+        <v>43.5</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
@@ -13891,7 +13851,7 @@
         </is>
       </c>
       <c r="K104" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L104" s="20" t="inlineStr">
         <is>
@@ -13900,7 +13860,7 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
@@ -13925,17 +13885,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -13944,7 +13904,7 @@
         </is>
       </c>
       <c r="G105" s="22" t="n">
-        <v>43.5</v>
+        <v>26.1</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
@@ -13963,7 +13923,7 @@
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
@@ -13983,50 +13943,50 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dřevěné stupně schodišť</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>26.1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
@@ -14051,26 +14011,26 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
-        </is>
-      </c>
-      <c r="D107" s="20" t="inlineStr">
-        <is>
-          <t>766811111</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D107" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="n">
-        <v>16</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
@@ -14080,16 +14040,16 @@
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
@@ -14109,55 +14069,55 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D108" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G108" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K108" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O108" s="26" t="inlineStr">
@@ -14177,7 +14137,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -14187,7 +14147,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -14196,7 +14156,7 @@
         </is>
       </c>
       <c r="G109" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="n"/>
@@ -14210,12 +14170,12 @@
       </c>
       <c r="L109" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
@@ -14240,7 +14200,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -14250,7 +14210,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -14259,7 +14219,7 @@
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -14278,7 +14238,7 @@
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -14303,7 +14263,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -14313,7 +14273,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -14322,7 +14282,7 @@
         </is>
       </c>
       <c r="G111" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -14341,7 +14301,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -14366,7 +14326,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -14376,7 +14336,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
@@ -14385,7 +14345,7 @@
         </is>
       </c>
       <c r="G112" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="10" t="n"/>
@@ -14404,7 +14364,7 @@
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
@@ -14429,7 +14389,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -14439,7 +14399,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -14467,7 +14427,7 @@
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -14492,7 +14452,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -14502,7 +14462,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -14511,7 +14471,7 @@
         </is>
       </c>
       <c r="G114" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
@@ -14530,7 +14490,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -14555,17 +14515,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -14574,17 +14534,17 @@
         </is>
       </c>
       <c r="G115" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -14593,7 +14553,7 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
@@ -14618,17 +14578,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -14637,17 +14597,17 @@
         </is>
       </c>
       <c r="G116" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="20" t="inlineStr">
         <is>
@@ -14656,12 +14616,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -14681,17 +14641,17 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -14700,13 +14660,13 @@
         </is>
       </c>
       <c r="G117" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K117" s="24" t="n">
@@ -14719,12 +14679,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -14744,17 +14704,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -14763,17 +14723,17 @@
         </is>
       </c>
       <c r="G118" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L118" s="20" t="inlineStr">
         <is>
@@ -14782,12 +14742,12 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O118" s="26" t="inlineStr">
@@ -14807,17 +14767,17 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -14826,17 +14786,17 @@
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
@@ -14845,7 +14805,7 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
@@ -14865,55 +14825,55 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G120" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="n"/>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K120" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L120" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O120" s="26" t="inlineStr">
@@ -14933,7 +14893,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -14943,7 +14903,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -14971,12 +14931,12 @@
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O121" s="26" t="inlineStr">
@@ -14996,26 +14956,26 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G122" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -15025,16 +14985,16 @@
         </is>
       </c>
       <c r="K122" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L122" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -15059,26 +15019,26 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G123" s="23" t="n">
-        <v>2</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G123" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
@@ -15097,7 +15057,7 @@
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
@@ -15117,55 +15077,55 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>18</v>
+        <v>171.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K124" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L124" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O124" s="26" t="inlineStr">
@@ -15185,17 +15145,17 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -15204,13 +15164,13 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>171.5</v>
+        <v>13.5</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K125" s="24" t="n">
@@ -15218,12 +15178,12 @@
       </c>
       <c r="L125" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -15248,7 +15208,7 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
@@ -15258,7 +15218,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -15267,7 +15227,7 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
@@ -15286,7 +15246,7 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
@@ -15311,17 +15271,17 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -15330,17 +15290,17 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>32.4</v>
+        <v>25</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K127" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L127" s="20" t="inlineStr">
         <is>
@@ -15349,12 +15309,12 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O127" s="26" t="inlineStr">
@@ -15374,17 +15334,17 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
@@ -15393,17 +15353,17 @@
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>25</v>
+        <v>126.4</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K128" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L128" s="20" t="inlineStr">
         <is>
@@ -15412,12 +15372,12 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O128" s="26" t="inlineStr">
@@ -15437,26 +15397,26 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>126.4</v>
+        <v>72.03</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
@@ -15475,12 +15435,12 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O129" s="26" t="inlineStr">
@@ -15500,17 +15460,17 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
@@ -15519,13 +15479,13 @@
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>72.03</v>
+        <v>19.28</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
@@ -15538,7 +15498,7 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
@@ -15558,41 +15518,41 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>19.28</v>
+        <v>78.2</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K131" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L131" s="20" t="inlineStr">
         <is>
@@ -15601,12 +15561,12 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O131" s="26" t="inlineStr">
@@ -15626,7 +15586,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -15636,7 +15596,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -15645,7 +15605,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -15664,7 +15624,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -15689,7 +15649,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -15699,7 +15659,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -15708,7 +15668,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -15727,7 +15687,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -15752,7 +15712,7 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
@@ -15762,7 +15722,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -15771,7 +15731,7 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
@@ -15790,7 +15750,7 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
@@ -15815,17 +15775,17 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
@@ -15834,17 +15794,17 @@
         </is>
       </c>
       <c r="G135" s="22" t="n">
-        <v>179.1</v>
+        <v>59.5</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K135" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L135" s="20" t="inlineStr">
         <is>
@@ -15853,12 +15813,12 @@
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O135" s="26" t="inlineStr">
@@ -15878,7 +15838,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
@@ -15888,7 +15848,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -15897,7 +15857,7 @@
         </is>
       </c>
       <c r="G136" s="22" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
@@ -15916,7 +15876,7 @@
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -15941,7 +15901,7 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
@@ -15951,7 +15911,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -15960,7 +15920,7 @@
         </is>
       </c>
       <c r="G137" s="22" t="n">
-        <v>61.1</v>
+        <v>64.5</v>
       </c>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="n"/>
@@ -15979,7 +15939,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
@@ -16004,17 +15964,17 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
@@ -16023,17 +15983,17 @@
         </is>
       </c>
       <c r="G138" s="22" t="n">
-        <v>64.5</v>
+        <v>13.4</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K138" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L138" s="20" t="inlineStr">
         <is>
@@ -16042,7 +16002,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -16067,7 +16027,7 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
@@ -16077,7 +16037,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
@@ -16086,7 +16046,7 @@
         </is>
       </c>
       <c r="G139" s="22" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -16105,7 +16065,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -16130,7 +16090,7 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
@@ -16140,7 +16100,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -16149,7 +16109,7 @@
         </is>
       </c>
       <c r="G140" s="22" t="n">
-        <v>15.2</v>
+        <v>24.3</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -16168,7 +16128,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -16193,7 +16153,7 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
@@ -16203,7 +16163,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -16212,7 +16172,7 @@
         </is>
       </c>
       <c r="G141" s="22" t="n">
-        <v>24.3</v>
+        <v>10</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
@@ -16222,7 +16182,7 @@
         </is>
       </c>
       <c r="K141" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L141" s="20" t="inlineStr">
         <is>
@@ -16231,7 +16191,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -16256,17 +16216,17 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
@@ -16275,17 +16235,17 @@
         </is>
       </c>
       <c r="G142" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -16294,7 +16254,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -16319,7 +16279,7 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
@@ -16329,7 +16289,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -16338,7 +16298,7 @@
         </is>
       </c>
       <c r="G143" s="22" t="n">
-        <v>0</v>
+        <v>254.5</v>
       </c>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="n"/>
@@ -16348,7 +16308,7 @@
         </is>
       </c>
       <c r="K143" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L143" s="20" t="inlineStr">
         <is>
@@ -16357,7 +16317,7 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
@@ -16382,7 +16342,7 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -16392,7 +16352,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -16401,7 +16361,7 @@
         </is>
       </c>
       <c r="G144" s="22" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="H144" s="10" t="n"/>
       <c r="I144" s="10" t="n"/>
@@ -16420,7 +16380,7 @@
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
@@ -16445,7 +16405,7 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
@@ -16455,7 +16415,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
@@ -16464,7 +16424,7 @@
         </is>
       </c>
       <c r="G145" s="22" t="n">
-        <v>78.2</v>
+        <v>247.5</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -16483,7 +16443,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -16508,7 +16468,7 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
@@ -16518,7 +16478,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
@@ -16527,7 +16487,7 @@
         </is>
       </c>
       <c r="G146" s="22" t="n">
-        <v>247.5</v>
+        <v>219.3</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
@@ -16546,7 +16506,7 @@
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -16566,37 +16526,37 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G147" s="22" t="n">
-        <v>219.3</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K147" s="24" t="n">
@@ -16604,12 +16564,12 @@
       </c>
       <c r="L147" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -16634,17 +16594,17 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
@@ -16653,13 +16613,13 @@
         </is>
       </c>
       <c r="G148" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H148" s="10" t="n"/>
       <c r="I148" s="10" t="n"/>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K148" s="24" t="n">
@@ -16667,12 +16627,12 @@
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
@@ -16697,22 +16657,22 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
@@ -16722,11 +16682,11 @@
       <c r="I149" s="10" t="n"/>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K149" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L149" s="20" t="inlineStr">
         <is>
@@ -16735,7 +16695,7 @@
       </c>
       <c r="M149" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N149" s="20" t="inlineStr">
@@ -16755,27 +16715,27 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
@@ -16785,11 +16745,11 @@
       <c r="I150" s="10" t="n"/>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K150" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L150" s="20" t="inlineStr">
         <is>
@@ -16798,12 +16758,12 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O150" s="26" t="inlineStr">
@@ -16823,26 +16783,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G151" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -16861,7 +16821,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -16886,26 +16846,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="n">
-        <v>4</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -16915,7 +16875,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -16924,7 +16884,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -16949,26 +16909,26 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G153" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="n">
+        <v>70</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -16987,7 +16947,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -17012,17 +16972,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -17031,7 +16991,7 @@
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -17050,7 +17010,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -17075,26 +17035,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -17104,7 +17064,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -17113,7 +17073,7 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
@@ -17138,17 +17098,17 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -17163,11 +17123,11 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -17176,12 +17136,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -17196,22 +17156,22 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -17226,25 +17186,25 @@
       <c r="I157" s="10" t="n"/>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O157" s="26" t="inlineStr">
@@ -17264,26 +17224,26 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G158" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G158" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -17293,7 +17253,7 @@
         </is>
       </c>
       <c r="K158" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
@@ -17302,7 +17262,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -17327,17 +17287,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -17346,7 +17306,7 @@
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -17360,12 +17320,12 @@
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -17390,26 +17350,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>set</t>
         </is>
       </c>
       <c r="G160" s="22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -17428,7 +17388,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -17453,26 +17413,26 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G161" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
@@ -17482,7 +17442,7 @@
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -17491,12 +17451,12 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O161" s="26" t="inlineStr">
@@ -17516,17 +17476,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -17579,17 +17539,17 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -17642,26 +17602,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G164" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -17671,7 +17631,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -17680,12 +17640,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -17705,26 +17665,26 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G165" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G165" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H165" s="10" t="n"/>
       <c r="I165" s="10" t="n"/>
@@ -17734,7 +17694,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -17743,12 +17703,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -17768,17 +17728,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -17831,17 +17791,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -17894,26 +17854,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G168" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G168" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -17923,7 +17883,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -17932,12 +17892,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -17957,26 +17917,26 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G169" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
@@ -17986,7 +17946,7 @@
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -17995,12 +17955,12 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O169" s="26" t="inlineStr">
@@ -18020,17 +17980,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -18083,17 +18043,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -18146,17 +18106,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -18165,7 +18125,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -18175,7 +18135,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -18184,12 +18144,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -18209,17 +18169,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -18228,7 +18188,7 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
@@ -18238,7 +18198,7 @@
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -18247,7 +18207,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -18272,17 +18232,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -18291,17 +18251,17 @@
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -18310,7 +18270,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -18335,17 +18295,17 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -18360,7 +18320,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -18373,7 +18333,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -18393,22 +18353,22 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -18423,7 +18383,7 @@
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
@@ -18436,7 +18396,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
@@ -18461,22 +18421,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -18490,7 +18450,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -18499,12 +18459,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -18524,22 +18484,22 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G178" s="23" t="n">
@@ -18553,7 +18513,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -18562,12 +18522,12 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O178" s="26" t="inlineStr">
@@ -18587,17 +18547,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -18625,7 +18585,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -18650,17 +18610,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -18675,7 +18635,7 @@
       <c r="I180" s="10" t="n"/>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K180" s="24" t="n">
@@ -18688,7 +18648,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -18713,17 +18673,17 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -18732,7 +18692,7 @@
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
@@ -18742,7 +18702,7 @@
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -18751,7 +18711,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -18776,36 +18736,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G182" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -18814,7 +18774,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -18839,36 +18799,36 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G183" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G183" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -18877,7 +18837,7 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
@@ -18897,41 +18857,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G184" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G184" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -18940,12 +18900,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -18960,22 +18920,22 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
@@ -19003,12 +18963,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -19023,41 +18983,41 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -19066,12 +19026,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -19091,36 +19051,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -19129,12 +19089,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -19154,36 +19114,36 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G188" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G188" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -19192,12 +19152,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -19212,41 +19172,41 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G189" s="22" t="n">
-        <v>56.9</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L189" s="20" t="inlineStr">
         <is>
@@ -19255,12 +19215,12 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O189" s="26" t="inlineStr">
@@ -19275,37 +19235,37 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G190" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K190" s="24" t="n">
@@ -19318,7 +19278,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -19338,31 +19298,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G191" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G191" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -19372,7 +19332,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -19381,7 +19341,7 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
@@ -19401,31 +19361,31 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G192" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G192" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H192" s="10" t="n"/>
       <c r="I192" s="10" t="n"/>
@@ -19435,7 +19395,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -19444,12 +19404,12 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O192" s="26" t="inlineStr">
@@ -19469,22 +19429,22 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
@@ -19498,7 +19458,7 @@
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -19507,7 +19467,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -19527,22 +19487,22 @@
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -19557,11 +19517,11 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L194" s="20" t="inlineStr">
         <is>
@@ -19570,7 +19530,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -19595,17 +19555,17 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
@@ -19620,7 +19580,7 @@
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
@@ -19633,7 +19593,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
@@ -19653,41 +19613,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G196" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G196" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -19696,12 +19656,12 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O196" s="26" t="inlineStr">
@@ -19716,41 +19676,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G197" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -19759,7 +19719,7 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
@@ -19779,41 +19739,41 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H198" s="10" t="n"/>
       <c r="I198" s="10" t="n"/>
       <c r="J198" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K198" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L198" s="20" t="inlineStr">
         <is>
@@ -19822,12 +19782,12 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O198" s="26" t="inlineStr">
@@ -19847,22 +19807,22 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
@@ -19885,7 +19845,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -19910,26 +19870,26 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G200" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H200" s="10" t="n"/>
       <c r="I200" s="10" t="n"/>
@@ -19948,7 +19908,7 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
@@ -19973,17 +19933,17 @@
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Voda staveniště</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
@@ -20002,7 +19962,7 @@
         </is>
       </c>
       <c r="K201" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L201" s="20" t="inlineStr">
         <is>
@@ -20011,12 +19971,12 @@
       </c>
       <c r="M201" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="N201" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O201" s="26" t="inlineStr">
@@ -20031,27 +19991,27 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
         </is>
       </c>
       <c r="D202" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="F202" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G202" s="23" t="n">
@@ -20061,11 +20021,11 @@
       <c r="I202" s="10" t="n"/>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektrikar</t>
         </is>
       </c>
       <c r="K202" s="24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L202" s="20" t="inlineStr">
         <is>
@@ -20074,7 +20034,7 @@
       </c>
       <c r="M202" s="8" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="N202" s="20" t="inlineStr">
@@ -20094,12 +20054,12 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D203" s="20" t="inlineStr">
@@ -20109,26 +20069,26 @@
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
         </is>
       </c>
       <c r="F203" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G203" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H203" s="10" t="n"/>
       <c r="I203" s="10" t="n"/>
       <c r="J203" s="8" t="inlineStr">
         <is>
-          <t>elektrikar</t>
+          <t>vzduchotechnik</t>
         </is>
       </c>
       <c r="K203" s="24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L203" s="20" t="inlineStr">
         <is>
@@ -20137,7 +20097,7 @@
       </c>
       <c r="M203" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="N203" s="20" t="inlineStr">
@@ -20151,72 +20111,9 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="20" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" s="8" t="inlineStr">
-        <is>
-          <t>M-24 VZT</t>
-        </is>
-      </c>
-      <c r="C204" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní</t>
-        </is>
-      </c>
-      <c r="D204" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E204" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
-        </is>
-      </c>
-      <c r="F204" s="20" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G204" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H204" s="10" t="n"/>
-      <c r="I204" s="10" t="n"/>
-      <c r="J204" s="8" t="inlineStr">
-        <is>
-          <t>vzduchotechnik</t>
-        </is>
-      </c>
-      <c r="K204" s="24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L204" s="20" t="inlineStr">
-        <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M204" s="8" t="inlineStr">
-        <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
-        </is>
-      </c>
-      <c r="N204" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O204" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O204"/>
-  <conditionalFormatting sqref="K2:K204">
+  <autoFilter ref="A1:O203"/>
+  <conditionalFormatting sqref="K2:K203">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -20,8 +20,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$132</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -987,11 +987,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 131 řádků.</t>
+          <t>HSV položkově (117 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 130 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (202 dum + 31 sklad = 233 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 31 sklad = 232 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>233 (202 dum + 31 sklad)</t>
+          <t>232 (201 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 118 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 117 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 155 needs_production_lookup (66.5 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 155 needs_production_lookup (66.8 %)</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>30 items (viz Otazky_pro_Karla docx)</t>
+          <t>31 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1160,10 +1160,10 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-233 položek celkem (202 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+232 položek celkem (201 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
-10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
+9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
 ÚRS kódy navrženy heuristikou. Part 5b WebSearch verified 12 codes / 8 unique families (viz Sheet 9 Var_F_URS_Verification_Trail). Wrong-leaf pattern identifikován: heuristika odhadne 6-cifernou rodinu správně v ~75 % případů, ale 9-cifrový leaf je chybný v ~63 % (odlišný distance band / materiál / geometrie / lokace). Produkční URS_MATCHER service (Perplexity-driven online lookup) nutný pro finální ověření zbývajících položek před cenotvorbou. Jednotkové ceny ponecháno k vyplnění zhotovitelem.</t>
         </is>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu; ETICS EPS 70F grey 160 mm; ETICS sokl XPS; Špalety EPS; … (+5 dalších)</t>
+          <t>Příprava podkladu; ETICS EPS 70F grey 160 mm; Špalety EPS; Profilace fasády; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
@@ -1988,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5751,16 +5751,16 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="F94" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622223111</t>
+          <t>URS-prop 622221221</t>
         </is>
       </c>
     </row>
@@ -5791,16 +5791,16 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="F95" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
@@ -5831,16 +5831,16 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="F96" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>276.7</v>
       </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221221</t>
+          <t>URS-prop 622521111</t>
         </is>
       </c>
     </row>
@@ -5866,32 +5866,32 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F97" s="22" t="n">
-        <v>290.2</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622521111</t>
+          <t>URS-prop 978013181</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="F98" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="F99" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 978013181</t>
+          <t>URS-prop 968072456</t>
         </is>
       </c>
     </row>
@@ -5991,16 +5991,16 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F100" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968072456</t>
+          <t>URS-prop 962024141</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
@@ -6040,7 +6040,7 @@
         </is>
       </c>
       <c r="F101" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 962024141</t>
+          <t>URS-prop 961044111</t>
         </is>
       </c>
     </row>
@@ -6066,32 +6066,32 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 961044111</t>
+          <t>URS-prop 877315111</t>
         </is>
       </c>
     </row>
@@ -6101,37 +6101,37 @@
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
+          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F103" s="22" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 877315111</t>
+          <t>URS-prop 121301101</t>
         </is>
       </c>
     </row>
@@ -6141,37 +6141,37 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>5.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F104" s="23" t="n">
+        <v>13</v>
       </c>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 121301101</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
@@ -6200,18 +6200,18 @@
         </is>
       </c>
       <c r="F105" s="23" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -6226,32 +6226,32 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
+          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F106" s="23" t="n">
-        <v>50</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>59.5</v>
       </c>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>tesar</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 762085112</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
+          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
+          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="F108" s="22" t="n">
-        <v>59.5</v>
+        <v>104.4</v>
       </c>
       <c r="G108" s="10" t="n"/>
       <c r="H108" s="10" t="n"/>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713121</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
+          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -6359,19 +6359,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F109" s="22" t="n">
-        <v>104.4</v>
-      </c>
+      <c r="F109" s="22" t="n"/>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713121</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6389,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
+          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -6404,12 +6402,12 @@
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6427,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
+          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -6442,12 +6440,12 @@
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6465,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
+          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -6500,12 +6498,12 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
+          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -6513,12 +6511,14 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F113" s="22" t="n"/>
+      <c r="F113" s="22" t="n">
+        <v>23</v>
+      </c>
       <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -6558,7 +6558,7 @@
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -6598,7 +6598,7 @@
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -6632,13 +6632,13 @@
         </is>
       </c>
       <c r="F116" s="22" t="n">
-        <v>23</v>
+        <v>140.94</v>
       </c>
       <c r="G116" s="10" t="n"/>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>pokryvac</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -6672,13 +6672,13 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>140.94</v>
+        <v>23</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>pokryvac</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
@@ -6693,17 +6693,17 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -6711,14 +6711,12 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F118" s="22" t="n">
-        <v>23</v>
-      </c>
+      <c r="F118" s="22" t="n"/>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -6736,32 +6734,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F119" s="22" t="n"/>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>agregát</t>
         </is>
       </c>
     </row>
@@ -6776,12 +6776,12 @@
       </c>
       <c r="C120" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -6851,17 +6851,17 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -7245,48 +7245,8 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="20" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="20" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C132" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr">
-        <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
-        </is>
-      </c>
-      <c r="E132" s="20" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="10" t="n"/>
-      <c r="H132" s="10" t="n"/>
-      <c r="I132" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J132" s="8" t="inlineStr">
-        <is>
-          <t>agregát</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J132"/>
+  <autoFilter ref="A1:J131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7297,7 +7257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O203"/>
+  <dimension ref="A1:O202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12857,7 +12817,7 @@
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#35</t>
         </is>
       </c>
       <c r="O88" s="26" t="inlineStr">
@@ -12983,7 +12943,7 @@
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#35</t>
         </is>
       </c>
       <c r="O90" s="26" t="inlineStr">
@@ -13129,26 +13089,26 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -13158,21 +13118,21 @@
         </is>
       </c>
       <c r="K93" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L93" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O93" s="26" t="inlineStr">
@@ -13192,7 +13152,7 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -13202,16 +13162,16 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
@@ -13230,12 +13190,12 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O94" s="26" t="inlineStr">
@@ -13255,26 +13215,26 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>276.7</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -13284,16 +13244,16 @@
         </is>
       </c>
       <c r="K95" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L95" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
@@ -13313,22 +13273,22 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
@@ -13337,17 +13297,17 @@
         </is>
       </c>
       <c r="G96" s="22" t="n">
-        <v>290.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
@@ -13356,12 +13316,12 @@
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O96" s="26" t="inlineStr">
@@ -13381,26 +13341,26 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Odvětrání radonu z podloží</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G97" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>12</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
@@ -13419,12 +13379,12 @@
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O97" s="26" t="inlineStr">
@@ -13444,26 +13404,26 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
-        </is>
-      </c>
-      <c r="D98" s="20" t="inlineStr">
-        <is>
-          <t>712381111</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+        </is>
+      </c>
+      <c r="D98" s="27" t="inlineStr">
+        <is>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G98" s="22" t="n">
-        <v>12</v>
+        <v>40.5</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -13473,7 +13433,7 @@
         </is>
       </c>
       <c r="K98" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L98" s="20" t="inlineStr">
         <is>
@@ -13482,12 +13442,12 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O98" s="26" t="inlineStr">
@@ -13502,22 +13462,22 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>711??? ?</t>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -13526,17 +13486,17 @@
         </is>
       </c>
       <c r="G99" s="22" t="n">
-        <v>40.5</v>
+        <v>177.5</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K99" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
@@ -13545,7 +13505,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
@@ -13570,7 +13530,7 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>Kročejová EPS nad ocelobeton</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
@@ -13580,7 +13540,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -13589,7 +13549,7 @@
         </is>
       </c>
       <c r="G100" s="22" t="n">
-        <v>177.5</v>
+        <v>104.4</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
@@ -13599,7 +13559,7 @@
         </is>
       </c>
       <c r="K100" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L100" s="20" t="inlineStr">
         <is>
@@ -13608,12 +13568,12 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O100" s="26" t="inlineStr">
@@ -13628,41 +13588,41 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
-        </is>
-      </c>
-      <c r="D101" s="27" t="inlineStr">
-        <is>
-          <t>713121??? ?</t>
+          <t>Oplechování krytiny</t>
+        </is>
+      </c>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G101" s="22" t="n">
-        <v>104.4</v>
+        <v>69.5</v>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K101" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L101" s="20" t="inlineStr">
         <is>
@@ -13671,12 +13631,12 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O101" s="26" t="inlineStr">
@@ -13696,17 +13656,17 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
@@ -13715,7 +13675,7 @@
         </is>
       </c>
       <c r="G102" s="22" t="n">
-        <v>69.5</v>
+        <v>20.8</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
@@ -13725,7 +13685,7 @@
         </is>
       </c>
       <c r="K102" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L102" s="20" t="inlineStr">
         <is>
@@ -13734,12 +13694,12 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O102" s="26" t="inlineStr">
@@ -13759,17 +13719,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -13778,7 +13738,7 @@
         </is>
       </c>
       <c r="G103" s="22" t="n">
-        <v>20.8</v>
+        <v>43.5</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
@@ -13788,7 +13748,7 @@
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -13797,7 +13757,7 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
@@ -13822,17 +13782,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -13841,7 +13801,7 @@
         </is>
       </c>
       <c r="G104" s="22" t="n">
-        <v>43.5</v>
+        <v>26.1</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
@@ -13860,7 +13820,7 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
@@ -13880,50 +13840,50 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dřevěné stupně schodišť</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>26.1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K105" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L105" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
@@ -13948,26 +13908,26 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
-        </is>
-      </c>
-      <c r="D106" s="20" t="inlineStr">
-        <is>
-          <t>766811111</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D106" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G106" s="23" t="n">
-        <v>16</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
@@ -13977,16 +13937,16 @@
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
@@ -14006,55 +13966,55 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D107" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G107" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O107" s="26" t="inlineStr">
@@ -14074,7 +14034,7 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -14084,7 +14044,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
@@ -14093,7 +14053,7 @@
         </is>
       </c>
       <c r="G108" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
@@ -14107,12 +14067,12 @@
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
@@ -14137,7 +14097,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -14147,7 +14107,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -14156,7 +14116,7 @@
         </is>
       </c>
       <c r="G109" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="n"/>
@@ -14175,7 +14135,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
@@ -14200,7 +14160,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -14210,7 +14170,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -14219,7 +14179,7 @@
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -14238,7 +14198,7 @@
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -14263,7 +14223,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -14273,7 +14233,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -14282,7 +14242,7 @@
         </is>
       </c>
       <c r="G111" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -14301,7 +14261,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -14326,7 +14286,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -14336,7 +14296,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
@@ -14364,7 +14324,7 @@
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
@@ -14389,7 +14349,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -14399,7 +14359,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -14408,7 +14368,7 @@
         </is>
       </c>
       <c r="G113" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="n"/>
@@ -14427,7 +14387,7 @@
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -14452,17 +14412,17 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -14471,17 +14431,17 @@
         </is>
       </c>
       <c r="G114" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K114" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L114" s="20" t="inlineStr">
         <is>
@@ -14490,7 +14450,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -14515,17 +14475,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -14534,17 +14494,17 @@
         </is>
       </c>
       <c r="G115" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -14553,12 +14513,12 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O115" s="26" t="inlineStr">
@@ -14578,17 +14538,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -14597,13 +14557,13 @@
         </is>
       </c>
       <c r="G116" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
@@ -14616,12 +14576,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -14641,17 +14601,17 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -14660,17 +14620,17 @@
         </is>
       </c>
       <c r="G117" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K117" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L117" s="20" t="inlineStr">
         <is>
@@ -14679,12 +14639,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -14704,17 +14664,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -14723,17 +14683,17 @@
         </is>
       </c>
       <c r="G118" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L118" s="20" t="inlineStr">
         <is>
@@ -14742,7 +14702,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
@@ -14762,55 +14722,55 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O119" s="26" t="inlineStr">
@@ -14830,7 +14790,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
@@ -14840,7 +14800,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
@@ -14868,12 +14828,12 @@
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O120" s="26" t="inlineStr">
@@ -14893,26 +14853,26 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G121" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="10" t="n"/>
@@ -14922,16 +14882,16 @@
         </is>
       </c>
       <c r="K121" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L121" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
@@ -14956,26 +14916,26 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G122" s="23" t="n">
-        <v>2</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -14994,7 +14954,7 @@
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -15014,55 +14974,55 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G123" s="22" t="n">
-        <v>18</v>
+        <v>171.5</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K123" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L123" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O123" s="26" t="inlineStr">
@@ -15082,17 +15042,17 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
@@ -15101,13 +15061,13 @@
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>171.5</v>
+        <v>13.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K124" s="24" t="n">
@@ -15115,12 +15075,12 @@
       </c>
       <c r="L124" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
@@ -15145,7 +15105,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -15155,7 +15115,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -15164,7 +15124,7 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
@@ -15183,7 +15143,7 @@
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -15208,17 +15168,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -15227,17 +15187,17 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>32.4</v>
+        <v>25</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K126" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L126" s="20" t="inlineStr">
         <is>
@@ -15246,12 +15206,12 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O126" s="26" t="inlineStr">
@@ -15271,17 +15231,17 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -15290,17 +15250,17 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>25</v>
+        <v>126.4</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K127" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L127" s="20" t="inlineStr">
         <is>
@@ -15309,12 +15269,12 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O127" s="26" t="inlineStr">
@@ -15334,26 +15294,26 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>126.4</v>
+        <v>72.03</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
@@ -15372,12 +15332,12 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O128" s="26" t="inlineStr">
@@ -15397,17 +15357,17 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
@@ -15416,13 +15376,13 @@
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>72.03</v>
+        <v>19.28</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K129" s="24" t="n">
@@ -15435,7 +15395,7 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
@@ -15455,41 +15415,41 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>19.28</v>
+        <v>78.2</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L130" s="20" t="inlineStr">
         <is>
@@ -15498,12 +15458,12 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O130" s="26" t="inlineStr">
@@ -15523,7 +15483,7 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
@@ -15533,7 +15493,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
@@ -15542,7 +15502,7 @@
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
@@ -15561,7 +15521,7 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
@@ -15586,7 +15546,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -15596,7 +15556,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -15605,7 +15565,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -15624,7 +15584,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -15649,7 +15609,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -15659,7 +15619,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -15668,7 +15628,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -15687,7 +15647,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -15712,17 +15672,17 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -15731,17 +15691,17 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>179.1</v>
+        <v>59.5</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K134" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L134" s="20" t="inlineStr">
         <is>
@@ -15750,12 +15710,12 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O134" s="26" t="inlineStr">
@@ -15775,7 +15735,7 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
@@ -15785,7 +15745,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
@@ -15794,7 +15754,7 @@
         </is>
       </c>
       <c r="G135" s="22" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
@@ -15813,7 +15773,7 @@
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
@@ -15838,7 +15798,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
@@ -15848,7 +15808,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -15857,7 +15817,7 @@
         </is>
       </c>
       <c r="G136" s="22" t="n">
-        <v>61.1</v>
+        <v>64.5</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
@@ -15876,7 +15836,7 @@
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -15901,17 +15861,17 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -15920,17 +15880,17 @@
         </is>
       </c>
       <c r="G137" s="22" t="n">
-        <v>64.5</v>
+        <v>13.4</v>
       </c>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K137" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L137" s="20" t="inlineStr">
         <is>
@@ -15939,7 +15899,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
@@ -15964,7 +15924,7 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
@@ -15974,7 +15934,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
@@ -15983,7 +15943,7 @@
         </is>
       </c>
       <c r="G138" s="22" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
@@ -16002,7 +15962,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -16027,7 +15987,7 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
@@ -16037,7 +15997,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
@@ -16046,7 +16006,7 @@
         </is>
       </c>
       <c r="G139" s="22" t="n">
-        <v>15.2</v>
+        <v>24.3</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -16065,7 +16025,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -16090,7 +16050,7 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
@@ -16100,7 +16060,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -16109,7 +16069,7 @@
         </is>
       </c>
       <c r="G140" s="22" t="n">
-        <v>24.3</v>
+        <v>10</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -16119,7 +16079,7 @@
         </is>
       </c>
       <c r="K140" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L140" s="20" t="inlineStr">
         <is>
@@ -16128,7 +16088,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -16153,17 +16113,17 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -16172,17 +16132,17 @@
         </is>
       </c>
       <c r="G141" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K141" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L141" s="20" t="inlineStr">
         <is>
@@ -16191,7 +16151,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -16216,7 +16176,7 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
@@ -16226,7 +16186,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
@@ -16235,7 +16195,7 @@
         </is>
       </c>
       <c r="G142" s="22" t="n">
-        <v>0</v>
+        <v>254.5</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
@@ -16245,7 +16205,7 @@
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -16254,7 +16214,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -16279,7 +16239,7 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
@@ -16289,7 +16249,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -16298,7 +16258,7 @@
         </is>
       </c>
       <c r="G143" s="22" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="n"/>
@@ -16317,7 +16277,7 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
@@ -16342,7 +16302,7 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -16352,7 +16312,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -16361,7 +16321,7 @@
         </is>
       </c>
       <c r="G144" s="22" t="n">
-        <v>78.2</v>
+        <v>247.5</v>
       </c>
       <c r="H144" s="10" t="n"/>
       <c r="I144" s="10" t="n"/>
@@ -16380,7 +16340,7 @@
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
@@ -16405,7 +16365,7 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
@@ -16415,7 +16375,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
@@ -16424,7 +16384,7 @@
         </is>
       </c>
       <c r="G145" s="22" t="n">
-        <v>247.5</v>
+        <v>219.3</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -16443,7 +16403,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -16463,37 +16423,37 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G146" s="22" t="n">
-        <v>219.3</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K146" s="24" t="n">
@@ -16501,12 +16461,12 @@
       </c>
       <c r="L146" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -16531,17 +16491,17 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
@@ -16550,13 +16510,13 @@
         </is>
       </c>
       <c r="G147" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K147" s="24" t="n">
@@ -16564,12 +16524,12 @@
       </c>
       <c r="L147" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -16594,22 +16554,22 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G148" s="23" t="n">
@@ -16619,11 +16579,11 @@
       <c r="I148" s="10" t="n"/>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K148" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
@@ -16632,7 +16592,7 @@
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
@@ -16652,27 +16612,27 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
@@ -16682,11 +16642,11 @@
       <c r="I149" s="10" t="n"/>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K149" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L149" s="20" t="inlineStr">
         <is>
@@ -16695,12 +16655,12 @@
       </c>
       <c r="M149" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N149" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O149" s="26" t="inlineStr">
@@ -16720,26 +16680,26 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H150" s="10" t="n"/>
       <c r="I150" s="10" t="n"/>
@@ -16758,7 +16718,7 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
@@ -16783,26 +16743,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G151" s="23" t="n">
-        <v>4</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G151" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -16812,7 +16772,7 @@
         </is>
       </c>
       <c r="K151" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L151" s="20" t="inlineStr">
         <is>
@@ -16821,7 +16781,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -16846,26 +16806,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G152" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>70</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -16884,7 +16844,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -16909,17 +16869,17 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
@@ -16928,7 +16888,7 @@
         </is>
       </c>
       <c r="G153" s="23" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -16947,7 +16907,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -16972,26 +16932,26 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -17001,7 +16961,7 @@
         </is>
       </c>
       <c r="K154" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L154" s="20" t="inlineStr">
         <is>
@@ -17010,7 +16970,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -17035,17 +16995,17 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
@@ -17060,11 +17020,11 @@
       <c r="I155" s="10" t="n"/>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -17073,12 +17033,12 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O155" s="26" t="inlineStr">
@@ -17093,22 +17053,22 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -17123,25 +17083,25 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -17161,26 +17121,26 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G157" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G157" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H157" s="10" t="n"/>
       <c r="I157" s="10" t="n"/>
@@ -17190,7 +17150,7 @@
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
@@ -17199,7 +17159,7 @@
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
@@ -17224,17 +17184,17 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
@@ -17243,7 +17203,7 @@
         </is>
       </c>
       <c r="G158" s="22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -17257,12 +17217,12 @@
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -17287,26 +17247,26 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>set</t>
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -17325,7 +17285,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -17350,26 +17310,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G160" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G160" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -17379,7 +17339,7 @@
         </is>
       </c>
       <c r="K160" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L160" s="20" t="inlineStr">
         <is>
@@ -17388,12 +17348,12 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O160" s="26" t="inlineStr">
@@ -17413,17 +17373,17 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
@@ -17476,17 +17436,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -17539,26 +17499,26 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G163" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G163" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H163" s="10" t="n"/>
       <c r="I163" s="10" t="n"/>
@@ -17568,7 +17528,7 @@
         </is>
       </c>
       <c r="K163" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L163" s="20" t="inlineStr">
         <is>
@@ -17577,12 +17537,12 @@
       </c>
       <c r="M163" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N163" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O163" s="26" t="inlineStr">
@@ -17602,26 +17562,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G164" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -17631,7 +17591,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -17640,12 +17600,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -17665,17 +17625,17 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
@@ -17728,17 +17688,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -17791,26 +17751,26 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G167" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G167" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H167" s="10" t="n"/>
       <c r="I167" s="10" t="n"/>
@@ -17820,7 +17780,7 @@
         </is>
       </c>
       <c r="K167" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L167" s="20" t="inlineStr">
         <is>
@@ -17829,12 +17789,12 @@
       </c>
       <c r="M167" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N167" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O167" s="26" t="inlineStr">
@@ -17854,26 +17814,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G168" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -17883,7 +17843,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -17892,12 +17852,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -17917,17 +17877,17 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
@@ -17980,17 +17940,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -18043,17 +18003,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -18062,7 +18022,7 @@
         </is>
       </c>
       <c r="G171" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H171" s="10" t="n"/>
       <c r="I171" s="10" t="n"/>
@@ -18072,7 +18032,7 @@
         </is>
       </c>
       <c r="K171" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L171" s="20" t="inlineStr">
         <is>
@@ -18081,12 +18041,12 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N171" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O171" s="26" t="inlineStr">
@@ -18106,17 +18066,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -18125,7 +18085,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -18135,7 +18095,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -18144,7 +18104,7 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
@@ -18169,17 +18129,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -18188,17 +18148,17 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -18207,7 +18167,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -18232,17 +18192,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -18257,7 +18217,7 @@
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
@@ -18270,7 +18230,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -18290,22 +18250,22 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -18320,7 +18280,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -18333,7 +18293,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -18358,22 +18318,22 @@
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G176" s="23" t="n">
@@ -18387,7 +18347,7 @@
         </is>
       </c>
       <c r="K176" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L176" s="20" t="inlineStr">
         <is>
@@ -18396,12 +18356,12 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O176" s="26" t="inlineStr">
@@ -18421,22 +18381,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -18450,7 +18410,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -18459,12 +18419,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -18484,17 +18444,17 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
@@ -18522,7 +18482,7 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
@@ -18547,17 +18507,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -18572,7 +18532,7 @@
       <c r="I179" s="10" t="n"/>
       <c r="J179" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K179" s="24" t="n">
@@ -18585,7 +18545,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -18610,17 +18570,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -18629,7 +18589,7 @@
         </is>
       </c>
       <c r="G180" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H180" s="10" t="n"/>
       <c r="I180" s="10" t="n"/>
@@ -18639,7 +18599,7 @@
         </is>
       </c>
       <c r="K180" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L180" s="20" t="inlineStr">
         <is>
@@ -18648,7 +18608,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -18673,36 +18633,36 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -18711,7 +18671,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -18736,36 +18696,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G182" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G182" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -18774,7 +18734,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -18794,41 +18754,41 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -18837,12 +18797,12 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O183" s="26" t="inlineStr">
@@ -18857,22 +18817,22 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
@@ -18900,12 +18860,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -18920,41 +18880,41 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H185" s="10" t="n"/>
       <c r="I185" s="10" t="n"/>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K185" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L185" s="20" t="inlineStr">
         <is>
@@ -18963,12 +18923,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -18988,36 +18948,36 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -19026,12 +18986,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -19051,36 +19011,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G187" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G187" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -19089,12 +19049,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -19109,41 +19069,41 @@
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G188" s="22" t="n">
-        <v>56.9</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G188" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -19152,12 +19112,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -19172,37 +19132,37 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G189" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
@@ -19215,7 +19175,7 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
@@ -19235,31 +19195,31 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G190" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G190" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
@@ -19269,7 +19229,7 @@
         </is>
       </c>
       <c r="K190" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L190" s="20" t="inlineStr">
         <is>
@@ -19278,7 +19238,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -19298,31 +19258,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G191" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -19332,7 +19292,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -19341,12 +19301,12 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O191" s="26" t="inlineStr">
@@ -19366,22 +19326,22 @@
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G192" s="23" t="n">
@@ -19395,7 +19355,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -19404,7 +19364,7 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
@@ -19424,22 +19384,22 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
@@ -19454,11 +19414,11 @@
       <c r="I193" s="10" t="n"/>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -19467,7 +19427,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -19492,17 +19452,17 @@
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -19517,7 +19477,7 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
@@ -19530,7 +19490,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -19550,41 +19510,41 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G195" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G195" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H195" s="10" t="n"/>
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L195" s="20" t="inlineStr">
         <is>
@@ -19593,12 +19553,12 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O195" s="26" t="inlineStr">
@@ -19613,41 +19573,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G196" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G196" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -19656,7 +19616,7 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
@@ -19676,41 +19636,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G197" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -19719,12 +19679,12 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O197" s="26" t="inlineStr">
@@ -19744,22 +19704,22 @@
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
@@ -19782,7 +19742,7 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
@@ -19807,26 +19767,26 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H199" s="10" t="n"/>
       <c r="I199" s="10" t="n"/>
@@ -19845,7 +19805,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -19870,17 +19830,17 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Voda staveniště</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
@@ -19899,7 +19859,7 @@
         </is>
       </c>
       <c r="K200" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L200" s="20" t="inlineStr">
         <is>
@@ -19908,12 +19868,12 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O200" s="26" t="inlineStr">
@@ -19928,27 +19888,27 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G201" s="23" t="n">
@@ -19958,11 +19918,11 @@
       <c r="I201" s="10" t="n"/>
       <c r="J201" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektrikar</t>
         </is>
       </c>
       <c r="K201" s="24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L201" s="20" t="inlineStr">
         <is>
@@ -19971,7 +19931,7 @@
       </c>
       <c r="M201" s="8" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="N201" s="20" t="inlineStr">
@@ -19991,12 +19951,12 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D202" s="20" t="inlineStr">
@@ -20006,26 +19966,26 @@
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
         </is>
       </c>
       <c r="F202" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G202" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H202" s="10" t="n"/>
       <c r="I202" s="10" t="n"/>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>elektrikar</t>
+          <t>vzduchotechnik</t>
         </is>
       </c>
       <c r="K202" s="24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L202" s="20" t="inlineStr">
         <is>
@@ -20034,7 +19994,7 @@
       </c>
       <c r="M202" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="N202" s="20" t="inlineStr">
@@ -20048,72 +20008,9 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="20" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" s="8" t="inlineStr">
-        <is>
-          <t>M-24 VZT</t>
-        </is>
-      </c>
-      <c r="C203" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní</t>
-        </is>
-      </c>
-      <c r="D203" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E203" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
-        </is>
-      </c>
-      <c r="F203" s="20" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G203" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H203" s="10" t="n"/>
-      <c r="I203" s="10" t="n"/>
-      <c r="J203" s="8" t="inlineStr">
-        <is>
-          <t>vzduchotechnik</t>
-        </is>
-      </c>
-      <c r="K203" s="24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L203" s="20" t="inlineStr">
-        <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M203" s="8" t="inlineStr">
-        <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
-        </is>
-      </c>
-      <c r="N203" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O203" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O203"/>
-  <conditionalFormatting sqref="K2:K203">
+  <autoFilter ref="A1:O202"/>
+  <conditionalFormatting sqref="K2:K202">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -20,9 +20,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,11 +987,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (117 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 130 řádků.</t>
+          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 31 sklad = 232 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 33 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>232 (201 dum + 31 sklad)</t>
+          <t>234 (201 dum + 33 sklad)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 117 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 155 needs_production_lookup (66.8 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 157 needs_production_lookup (67.1 %)</t>
         </is>
       </c>
     </row>
@@ -1160,8 +1160,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-232 položek celkem (201 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1837,11 +1837,11 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna; Tvarovky ZB obvod skladu; Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna; Tvarovky ZB obvod skladu; Výztuž ZB tvarovek; Hydroizolace + protiradon stěn pod terénem (S03a+S04); … (+1 dalších)</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="n"/>
@@ -1988,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="F33" s="22" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="F59" s="22" t="n">
-        <v>33.9</v>
+        <v>36.74</v>
       </c>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="F113" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="F114" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="F115" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G115" s="10" t="n"/>
       <c r="H115" s="10" t="n"/>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
@@ -6734,34 +6734,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C119" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04) — Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>33</v>
       </c>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6774,34 +6774,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04) — Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>33</v>
       </c>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -6816,12 +6816,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -6851,17 +6851,17 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -6891,17 +6891,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -7245,8 +7245,88 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12730,7 +12810,7 @@
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
@@ -12793,7 +12873,7 @@
         </is>
       </c>
       <c r="G88" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H88" s="10" t="n"/>
       <c r="I88" s="10" t="n"/>
@@ -12856,7 +12936,7 @@
         </is>
       </c>
       <c r="G89" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
@@ -12919,7 +12999,7 @@
         </is>
       </c>
       <c r="G90" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H90" s="10" t="n"/>
       <c r="I90" s="10" t="n"/>
@@ -20028,12 +20108,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -20407,7 +20487,7 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
@@ -20784,7 +20864,7 @@
         </is>
       </c>
       <c r="G12" s="22" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n"/>
@@ -21075,41 +21155,41 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -21118,7 +21198,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -21138,22 +21218,22 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -21162,17 +21242,17 @@
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>21.209</v>
+        <v>33</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
@@ -21181,7 +21261,7 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -21206,32 +21286,32 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
@@ -21244,7 +21324,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
+          <t>TZ statika sklad §4 + DXF DIMENSION</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -21269,36 +21349,36 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>921</v>
+        <v>21.209</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
@@ -21307,12 +21387,12 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 + DXF LWPOLYLINE 7000 mm + rozteč 1000 mm</t>
+          <t>TZ statika sklad §4 + DXF</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -21332,17 +21412,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -21351,26 +21431,26 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §4 — HI souvrství</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -21395,17 +21475,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -21414,7 +21494,7 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>1551</v>
+        <v>921</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
@@ -21424,7 +21504,7 @@
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -21433,12 +21513,12 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 + ČSN EN ISO 12944 — žárový zinek pro pojezdové ocel</t>
+          <t>TZ statika sklad §1.4 + DXF LWPOLYLINE 7000 mm + rozteč 1000 mm</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -21453,22 +21533,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -21477,26 +21557,26 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -21516,39 +21596,41 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="n">
+        <v>1551</v>
+      </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
@@ -21557,7 +21639,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>TZ statika sklad §1.4 + ČSN EN ISO 12944 — žárový zinek pro pojezdové ocel</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -21577,41 +21659,41 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Sklad mezipodesta schodiště prefa</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G25" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
@@ -21620,7 +21702,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -21640,12 +21722,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -21655,26 +21737,24 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="n"/>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
@@ -21683,7 +21763,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -21703,50 +21783,50 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G27" s="22" t="n">
-        <v>17.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -21754,9 +21834,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O27" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -21766,27 +21846,27 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G28" s="23" t="n">
@@ -21796,11 +21876,11 @@
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
@@ -21809,7 +21889,7 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -21829,50 +21909,50 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>8</v>
+        <v>17.6</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -21880,9 +21960,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O29" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O29" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
       </c>
     </row>
@@ -21892,22 +21972,22 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -21922,11 +22002,11 @@
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
@@ -21935,7 +22015,7 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
@@ -21955,41 +22035,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -21998,7 +22078,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -22018,27 +22098,27 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Geodetické vytýčení sklad</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G32" s="23" t="n">
@@ -22048,36 +22128,162 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+        </is>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O32" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
           <t>VRN_management</t>
         </is>
       </c>
-      <c r="K32" s="24" t="n">
+      <c r="K34" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="L32" s="20" t="inlineStr">
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M32" s="8" t="inlineStr">
+      <c r="M34" s="8" t="inlineStr">
         <is>
           <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
         </is>
       </c>
-      <c r="N32" s="20" t="inlineStr">
+      <c r="N34" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O32" s="26" t="inlineStr">
+      <c r="O34" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O32"/>
-  <conditionalFormatting sqref="K2:K32">
+  <autoFilter ref="A1:O34"/>
+  <conditionalFormatting sqref="K2:K34">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -21009,7 +21009,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — Herkul H-BLOK, montáž auto s hyd. rukou</t>
+          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.82: 1 | 0.80: 21 | 0.75: 70 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
 234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 1×0.82 · 21×0.80 · 70×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="F42" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
@@ -20990,7 +20990,7 @@
         </is>
       </c>
       <c r="G14" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
+          <t>TZ statika sklad §[19] + web: H-BLOK Standard Herkul (Obrnice) líc 1800×600 mm = 1.08 m²/blok; ověřit definitiv z tech. listu dodavatele</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -21009,7 +21009,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] + web: H-BLOK Standard Herkul (Obrnice) líc 1800×600 mm = 1.08 m²/blok; ověřit definitiv z tech. listu dodavatele</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul (Obrnice). Rozměr bloku NEověřen z tech. listu — odhad 1800×600 mm z web-analogie (BB6 stejný gabarit). Plocha líce 19.05 m² je measured (řez A-A); count 18 ks je estimate závislý na rozměru bloku.</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01.xlsx
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.82: 1 | 0.80: 21 | 0.75: 70 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
 234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 1×0.82 · 21×0.80 · 70×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="F42" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
@@ -20990,7 +20990,7 @@
         </is>
       </c>
       <c r="G14" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul (Obrnice). Rozměr bloku NEověřen z tech. listu — odhad 1800×600 mm z web-analogie (BB6 stejný gabarit). Plocha líce 19.05 m² je measured (řez A-A); count 18 ks je estimate závislý na rozměru bloku.</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
